--- a/research/traditional_assets/database/data/philippines/philippines_building_materials.xlsx
+++ b/research/traditional_assets/database/data/philippines/philippines_building_materials.xlsx
@@ -1278,7 +1278,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1415,22 +1415,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.1090672306419366</v>
+        <v>0.1088283125653318</v>
       </c>
       <c r="C2">
-        <v>95.10415847987514</v>
+        <v>94.20945889383019</v>
       </c>
       <c r="D2">
-        <v>58.80415847987515</v>
+        <v>58.86095889383019</v>
       </c>
       <c r="E2">
-        <v>-4.45</v>
+        <v>-3.4985</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>0.9515000000000001</v>
       </c>
       <c r="G2">
         <v>36.3</v>
@@ -1451,28 +1451,28 @@
         <v>26.4</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.04786045000000001</v>
       </c>
       <c r="N2">
-        <v>26.4</v>
+        <v>26.35213955</v>
       </c>
       <c r="O2">
-        <v>6.6</v>
+        <v>6.588034887499999</v>
       </c>
       <c r="P2">
-        <v>19.8</v>
+        <v>19.7641046625</v>
       </c>
       <c r="Q2">
-        <v>22.3</v>
+        <v>22.2641046625</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.1090672306419366</v>
+        <v>0.1095465278437695</v>
       </c>
       <c r="T2">
-        <v>0.920615294616134</v>
+        <v>0.9275896529086805</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1489,7 +1489,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>551.6036727611209</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1497,22 +1497,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.1088283125653318</v>
+        <v>0.108589394488727</v>
       </c>
       <c r="C3">
-        <v>94.20945889383019</v>
+        <v>93.31486914377213</v>
       </c>
       <c r="D3">
-        <v>58.86095889383019</v>
+        <v>58.91786914377213</v>
       </c>
       <c r="E3">
-        <v>-3.4985</v>
+        <v>-2.547</v>
       </c>
       <c r="F3">
-        <v>0.9515000000000001</v>
+        <v>1.903</v>
       </c>
       <c r="G3">
         <v>36.3</v>
@@ -1533,28 +1533,28 @@
         <v>26.4</v>
       </c>
       <c r="M3">
-        <v>0.04786045000000001</v>
+        <v>0.09572090000000001</v>
       </c>
       <c r="N3">
-        <v>26.35213955</v>
+        <v>26.3042791</v>
       </c>
       <c r="O3">
-        <v>6.588034887499999</v>
+        <v>6.576069775</v>
       </c>
       <c r="P3">
-        <v>19.7641046625</v>
+        <v>19.728209325</v>
       </c>
       <c r="Q3">
-        <v>22.2641046625</v>
+        <v>22.228209325</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.1095465278437695</v>
+        <v>0.1100356066211499</v>
       </c>
       <c r="T3">
-        <v>0.9275896529086805</v>
+        <v>0.934706345043932</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1571,7 +1571,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>551.6036727611209</v>
+        <v>275.8018363805605</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1579,22 +1579,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.108589394488727</v>
+        <v>0.1083504764121221</v>
       </c>
       <c r="C4">
-        <v>93.31486914377213</v>
+        <v>92.42038954859704</v>
       </c>
       <c r="D4">
-        <v>58.91786914377213</v>
+        <v>58.97488954859705</v>
       </c>
       <c r="E4">
-        <v>-2.547</v>
+        <v>-1.5955</v>
       </c>
       <c r="F4">
-        <v>1.903</v>
+        <v>2.8545</v>
       </c>
       <c r="G4">
         <v>36.3</v>
@@ -1615,28 +1615,28 @@
         <v>26.4</v>
       </c>
       <c r="M4">
-        <v>0.09572090000000001</v>
+        <v>0.14358135</v>
       </c>
       <c r="N4">
-        <v>26.3042791</v>
+        <v>26.25641865</v>
       </c>
       <c r="O4">
-        <v>6.576069775</v>
+        <v>6.564104662499999</v>
       </c>
       <c r="P4">
-        <v>19.728209325</v>
+        <v>19.6923139875</v>
       </c>
       <c r="Q4">
-        <v>22.228209325</v>
+        <v>22.1923139875</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.1100356066211499</v>
+        <v>0.1105347694970331</v>
       </c>
       <c r="T4">
-        <v>0.934706345043932</v>
+        <v>0.9419697730994978</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1653,7 +1653,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>275.8018363805605</v>
+        <v>183.8678909203737</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1661,22 +1661,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.1083504764121221</v>
+        <v>0.1081115583355172</v>
       </c>
       <c r="C5">
-        <v>92.42038954859704</v>
+        <v>91.52602042843672</v>
       </c>
       <c r="D5">
-        <v>58.97488954859705</v>
+        <v>59.03202042843672</v>
       </c>
       <c r="E5">
-        <v>-1.5955</v>
+        <v>-0.6439999999999997</v>
       </c>
       <c r="F5">
-        <v>2.8545</v>
+        <v>3.806</v>
       </c>
       <c r="G5">
         <v>36.3</v>
@@ -1697,28 +1697,28 @@
         <v>26.4</v>
       </c>
       <c r="M5">
-        <v>0.14358135</v>
+        <v>0.1914418</v>
       </c>
       <c r="N5">
-        <v>26.25641865</v>
+        <v>26.2085582</v>
       </c>
       <c r="O5">
-        <v>6.564104662499999</v>
+        <v>6.55213955</v>
       </c>
       <c r="P5">
-        <v>19.6923139875</v>
+        <v>19.65641865</v>
       </c>
       <c r="Q5">
-        <v>22.1923139875</v>
+        <v>22.15641865</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.1105347694970331</v>
+        <v>0.1110443315994971</v>
       </c>
       <c r="T5">
-        <v>0.9419697730994978</v>
+        <v>0.9493845225728882</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1735,7 +1735,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>183.8678909203737</v>
+        <v>137.9009181902803</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1743,22 +1743,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.1081115583355172</v>
+        <v>0.1078726402589124</v>
       </c>
       <c r="C6">
-        <v>91.52602042843672</v>
+        <v>90.63176210466463</v>
       </c>
       <c r="D6">
-        <v>59.03202042843672</v>
+        <v>59.08926210466462</v>
       </c>
       <c r="E6">
-        <v>-0.6439999999999997</v>
+        <v>0.3075000000000001</v>
       </c>
       <c r="F6">
-        <v>3.806</v>
+        <v>4.7575</v>
       </c>
       <c r="G6">
         <v>36.3</v>
@@ -1779,28 +1779,28 @@
         <v>26.4</v>
       </c>
       <c r="M6">
-        <v>0.1914418</v>
+        <v>0.23930225</v>
       </c>
       <c r="N6">
-        <v>26.2085582</v>
+        <v>26.16069775</v>
       </c>
       <c r="O6">
-        <v>6.55213955</v>
+        <v>6.540174437499999</v>
       </c>
       <c r="P6">
-        <v>19.65641865</v>
+        <v>19.6205233125</v>
       </c>
       <c r="Q6">
-        <v>22.15641865</v>
+        <v>22.1205233125</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.1110443315994971</v>
+        <v>0.111564621325171</v>
       </c>
       <c r="T6">
-        <v>0.9493845225728882</v>
+        <v>0.956955372035192</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1817,7 +1817,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>137.9009181902803</v>
+        <v>110.3207345522242</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1825,22 +1825,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.1078726402589124</v>
+        <v>0.1076337221823075</v>
       </c>
       <c r="C7">
-        <v>90.63176210466463</v>
+        <v>89.73761489990191</v>
       </c>
       <c r="D7">
-        <v>59.08926210466462</v>
+        <v>59.14661489990192</v>
       </c>
       <c r="E7">
-        <v>0.3075000000000001</v>
+        <v>1.259</v>
       </c>
       <c r="F7">
-        <v>4.7575</v>
+        <v>5.709000000000001</v>
       </c>
       <c r="G7">
         <v>36.3</v>
@@ -1861,28 +1861,28 @@
         <v>26.4</v>
       </c>
       <c r="M7">
-        <v>0.23930225</v>
+        <v>0.2871627</v>
       </c>
       <c r="N7">
-        <v>26.16069775</v>
+        <v>26.1128373</v>
       </c>
       <c r="O7">
-        <v>6.540174437499999</v>
+        <v>6.528209325</v>
       </c>
       <c r="P7">
-        <v>19.6205233125</v>
+        <v>19.584627975</v>
       </c>
       <c r="Q7">
-        <v>22.1205233125</v>
+        <v>22.084627975</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.111564621325171</v>
+        <v>0.112095981045008</v>
       </c>
       <c r="T7">
-        <v>0.956955372035192</v>
+        <v>0.9646873034009489</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1899,7 +1899,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>110.3207345522242</v>
+        <v>91.93394546018685</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1907,22 +1907,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.1076337221823075</v>
+        <v>0.1073948041057027</v>
       </c>
       <c r="C8">
-        <v>89.73761489990191</v>
+        <v>88.84357913802357</v>
       </c>
       <c r="D8">
-        <v>59.14661489990192</v>
+        <v>59.20407913802358</v>
       </c>
       <c r="E8">
-        <v>1.259</v>
+        <v>2.2105</v>
       </c>
       <c r="F8">
-        <v>5.709000000000001</v>
+        <v>6.6605</v>
       </c>
       <c r="G8">
         <v>36.3</v>
@@ -1943,28 +1943,28 @@
         <v>26.4</v>
       </c>
       <c r="M8">
-        <v>0.2871627</v>
+        <v>0.33502315</v>
       </c>
       <c r="N8">
-        <v>26.1128373</v>
+        <v>26.06497685</v>
       </c>
       <c r="O8">
-        <v>6.528209325</v>
+        <v>6.516244212499999</v>
       </c>
       <c r="P8">
-        <v>19.584627975</v>
+        <v>19.5487326375</v>
       </c>
       <c r="Q8">
-        <v>22.084627975</v>
+        <v>22.0487326375</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.112095981045008</v>
+        <v>0.1126387678555943</v>
       </c>
       <c r="T8">
-        <v>0.9646873034009489</v>
+        <v>0.9725855128605931</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1981,7 +1981,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>91.93394546018685</v>
+        <v>78.80052468016015</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1989,22 +1989,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.1073948041057027</v>
+        <v>0.1071558860290979</v>
       </c>
       <c r="C9">
-        <v>88.84357913802357</v>
+        <v>87.94965514416444</v>
       </c>
       <c r="D9">
-        <v>59.20407913802358</v>
+        <v>59.26165514416444</v>
       </c>
       <c r="E9">
-        <v>2.210500000000001</v>
+        <v>3.162000000000001</v>
       </c>
       <c r="F9">
-        <v>6.660500000000001</v>
+        <v>7.612000000000001</v>
       </c>
       <c r="G9">
         <v>36.3</v>
@@ -2025,28 +2025,28 @@
         <v>26.4</v>
       </c>
       <c r="M9">
-        <v>0.33502315</v>
+        <v>0.3828836</v>
       </c>
       <c r="N9">
-        <v>26.06497685</v>
+        <v>26.0171164</v>
       </c>
       <c r="O9">
-        <v>6.516244212499999</v>
+        <v>6.5042791</v>
       </c>
       <c r="P9">
-        <v>19.5487326375</v>
+        <v>19.5128373</v>
       </c>
       <c r="Q9">
-        <v>22.0487326375</v>
+        <v>22.0128373</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.1126387678555943</v>
+        <v>0.1131933543794542</v>
       </c>
       <c r="T9">
-        <v>0.9725855128605931</v>
+        <v>0.9806554225258819</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2063,7 +2063,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>78.80052468016014</v>
+        <v>68.95045909514013</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2071,22 +2071,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.1071558860290979</v>
+        <v>0.1069169679524931</v>
       </c>
       <c r="C10">
-        <v>87.94965514416444</v>
+        <v>87.05584324472534</v>
       </c>
       <c r="D10">
-        <v>59.26165514416444</v>
+        <v>59.31934324472535</v>
       </c>
       <c r="E10">
-        <v>3.162000000000001</v>
+        <v>4.113499999999999</v>
       </c>
       <c r="F10">
-        <v>7.612000000000001</v>
+        <v>8.563499999999999</v>
       </c>
       <c r="G10">
         <v>36.3</v>
@@ -2107,28 +2107,28 @@
         <v>26.4</v>
       </c>
       <c r="M10">
-        <v>0.3828836</v>
+        <v>0.4307440499999999</v>
       </c>
       <c r="N10">
-        <v>26.0171164</v>
+        <v>25.96925595</v>
       </c>
       <c r="O10">
-        <v>6.5042791</v>
+        <v>6.492313987499999</v>
       </c>
       <c r="P10">
-        <v>19.5128373</v>
+        <v>19.4769419625</v>
       </c>
       <c r="Q10">
-        <v>22.0128373</v>
+        <v>21.9769419625</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.1131933543794542</v>
+        <v>0.1137601296181242</v>
       </c>
       <c r="T10">
-        <v>0.9806554225258819</v>
+        <v>0.9889026928431549</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2145,7 +2145,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>68.95045909514013</v>
+        <v>61.28929697345791</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2153,22 +2153,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.1069169679524931</v>
+        <v>0.1066780498758882</v>
       </c>
       <c r="C11">
-        <v>87.05584324472534</v>
+        <v>86.16214376737932</v>
       </c>
       <c r="D11">
-        <v>59.31934324472535</v>
+        <v>59.37714376737932</v>
       </c>
       <c r="E11">
-        <v>4.113499999999999</v>
+        <v>5.065</v>
       </c>
       <c r="F11">
-        <v>8.563499999999999</v>
+        <v>9.515000000000001</v>
       </c>
       <c r="G11">
         <v>36.3</v>
@@ -2189,28 +2189,28 @@
         <v>26.4</v>
       </c>
       <c r="M11">
-        <v>0.4307440499999999</v>
+        <v>0.4786045</v>
       </c>
       <c r="N11">
-        <v>25.96925595</v>
+        <v>25.9213955</v>
       </c>
       <c r="O11">
-        <v>6.492313987499999</v>
+        <v>6.480348875</v>
       </c>
       <c r="P11">
-        <v>19.4769419625</v>
+        <v>19.441046625</v>
       </c>
       <c r="Q11">
-        <v>21.9769419625</v>
+        <v>21.941046625</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.1137601296181242</v>
+        <v>0.114339499862098</v>
       </c>
       <c r="T11">
-        <v>0.9889026928431549</v>
+        <v>0.9973332358341451</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2227,7 +2227,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>61.28929697345791</v>
+        <v>55.16036727611211</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2235,22 +2235,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.1066780498758882</v>
+        <v>0.1064391317992834</v>
       </c>
       <c r="C12">
-        <v>86.16214376737932</v>
+        <v>85.26855704107774</v>
       </c>
       <c r="D12">
-        <v>59.37714376737932</v>
+        <v>59.43505704107775</v>
       </c>
       <c r="E12">
-        <v>5.065</v>
+        <v>6.0165</v>
       </c>
       <c r="F12">
-        <v>9.515000000000001</v>
+        <v>10.4665</v>
       </c>
       <c r="G12">
         <v>36.3</v>
@@ -2271,28 +2271,28 @@
         <v>26.4</v>
       </c>
       <c r="M12">
-        <v>0.4786045</v>
+        <v>0.5264649499999999</v>
       </c>
       <c r="N12">
-        <v>25.9213955</v>
+        <v>25.87353505</v>
       </c>
       <c r="O12">
-        <v>6.480348875</v>
+        <v>6.468383762499999</v>
       </c>
       <c r="P12">
-        <v>19.441046625</v>
+        <v>19.4051512875</v>
       </c>
       <c r="Q12">
-        <v>21.941046625</v>
+        <v>21.9051512875</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.114339499862098</v>
+        <v>0.1149318896621161</v>
       </c>
       <c r="T12">
-        <v>0.9973332358341451</v>
+        <v>1.005953229229427</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2309,7 +2309,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>55.16036727611211</v>
+        <v>50.14578843282919</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2317,22 +2317,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.1064391317992834</v>
+        <v>0.1062002137226785</v>
       </c>
       <c r="C13">
-        <v>85.26855704107774</v>
+        <v>84.37508339605662</v>
       </c>
       <c r="D13">
-        <v>59.43505704107775</v>
+        <v>59.49308339605664</v>
       </c>
       <c r="E13">
-        <v>6.0165</v>
+        <v>6.968000000000001</v>
       </c>
       <c r="F13">
-        <v>10.4665</v>
+        <v>11.418</v>
       </c>
       <c r="G13">
         <v>36.3</v>
@@ -2353,28 +2353,28 @@
         <v>26.4</v>
       </c>
       <c r="M13">
-        <v>0.5264649499999999</v>
+        <v>0.5743254</v>
       </c>
       <c r="N13">
-        <v>25.87353505</v>
+        <v>25.8256746</v>
       </c>
       <c r="O13">
-        <v>6.468383762499999</v>
+        <v>6.45641865</v>
       </c>
       <c r="P13">
-        <v>19.4051512875</v>
+        <v>19.36925595</v>
       </c>
       <c r="Q13">
-        <v>21.9051512875</v>
+        <v>21.86925595</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.1149318896621161</v>
+        <v>0.1155377428666801</v>
       </c>
       <c r="T13">
-        <v>1.005953229229427</v>
+        <v>1.014769131565511</v>
       </c>
       <c r="U13">
         <v>0.0503</v>
@@ -2391,7 +2391,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>50.14578843282919</v>
+        <v>45.96697273009343</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2399,22 +2399,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.1062002137226785</v>
+        <v>0.1059612956460737</v>
       </c>
       <c r="C14">
-        <v>84.37508339605662</v>
+        <v>83.48172316384293</v>
       </c>
       <c r="D14">
-        <v>59.49308339605664</v>
+        <v>59.55122316384293</v>
       </c>
       <c r="E14">
-        <v>6.968000000000001</v>
+        <v>7.9195</v>
       </c>
       <c r="F14">
-        <v>11.418</v>
+        <v>12.3695</v>
       </c>
       <c r="G14">
         <v>36.3</v>
@@ -2435,28 +2435,28 @@
         <v>26.4</v>
       </c>
       <c r="M14">
-        <v>0.5743254</v>
+        <v>0.62218585</v>
       </c>
       <c r="N14">
-        <v>25.8256746</v>
+        <v>25.77781415</v>
       </c>
       <c r="O14">
-        <v>6.45641865</v>
+        <v>6.444453537499999</v>
       </c>
       <c r="P14">
-        <v>19.36925595</v>
+        <v>19.3333606125</v>
       </c>
       <c r="Q14">
-        <v>21.86925595</v>
+        <v>21.8333606125</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.1155377428666801</v>
+        <v>0.1161575237311192</v>
       </c>
       <c r="T14">
-        <v>1.014769131565511</v>
+        <v>1.023787698323114</v>
       </c>
       <c r="U14">
         <v>0.0503</v>
@@ -2473,7 +2473,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>45.96697273009343</v>
+        <v>42.43105175085547</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2481,22 +2481,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.1059612956460737</v>
+        <v>0.1057223775694688</v>
       </c>
       <c r="C15">
-        <v>83.48172316384293</v>
+        <v>82.58847667726074</v>
       </c>
       <c r="D15">
-        <v>59.55122316384293</v>
+        <v>59.60947667726074</v>
       </c>
       <c r="E15">
-        <v>7.9195</v>
+        <v>8.871000000000002</v>
       </c>
       <c r="F15">
-        <v>12.3695</v>
+        <v>13.321</v>
       </c>
       <c r="G15">
         <v>36.3</v>
@@ -2517,28 +2517,28 @@
         <v>26.4</v>
       </c>
       <c r="M15">
-        <v>0.62218585</v>
+        <v>0.6700463000000001</v>
       </c>
       <c r="N15">
-        <v>25.77781415</v>
+        <v>25.7299537</v>
       </c>
       <c r="O15">
-        <v>6.444453537499999</v>
+        <v>6.432488425</v>
       </c>
       <c r="P15">
-        <v>19.3333606125</v>
+        <v>19.297465275</v>
       </c>
       <c r="Q15">
-        <v>21.8333606125</v>
+        <v>21.797465275</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.1161575237311192</v>
+        <v>0.1167917181040335</v>
       </c>
       <c r="T15">
-        <v>1.023787698323114</v>
+        <v>1.03301599919136</v>
       </c>
       <c r="U15">
         <v>0.0503</v>
@@ -2555,7 +2555,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>42.43105175085547</v>
+        <v>39.40026234008008</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2563,22 +2563,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.1057223775694688</v>
+        <v>0.105483459492864</v>
       </c>
       <c r="C16">
-        <v>82.58847667726074</v>
+        <v>81.69534427043769</v>
       </c>
       <c r="D16">
-        <v>59.60947667726074</v>
+        <v>59.6678442704377</v>
       </c>
       <c r="E16">
-        <v>8.871000000000002</v>
+        <v>9.822500000000002</v>
       </c>
       <c r="F16">
-        <v>13.321</v>
+        <v>14.2725</v>
       </c>
       <c r="G16">
         <v>36.3</v>
@@ -2599,28 +2599,28 @@
         <v>26.4</v>
       </c>
       <c r="M16">
-        <v>0.6700463000000001</v>
+        <v>0.7179067500000001</v>
       </c>
       <c r="N16">
-        <v>25.7299537</v>
+        <v>25.68209325</v>
       </c>
       <c r="O16">
-        <v>6.432488425</v>
+        <v>6.420523312499999</v>
       </c>
       <c r="P16">
-        <v>19.297465275</v>
+        <v>19.2615699375</v>
       </c>
       <c r="Q16">
-        <v>21.797465275</v>
+        <v>21.7615699375</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.1167917181040335</v>
+        <v>0.1174408346974871</v>
       </c>
       <c r="T16">
-        <v>1.03301599919136</v>
+        <v>1.042461436550622</v>
       </c>
       <c r="U16">
         <v>0.0503</v>
@@ -2637,7 +2637,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>39.40026234008008</v>
+        <v>36.77357818407473</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2645,22 +2645,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.105483459492864</v>
+        <v>0.1052445414162591</v>
       </c>
       <c r="C17">
-        <v>81.69534427043769</v>
+        <v>80.80232627881151</v>
       </c>
       <c r="D17">
-        <v>59.6678442704377</v>
+        <v>59.72632627881151</v>
       </c>
       <c r="E17">
-        <v>9.822500000000002</v>
+        <v>10.774</v>
       </c>
       <c r="F17">
-        <v>14.2725</v>
+        <v>15.224</v>
       </c>
       <c r="G17">
         <v>36.3</v>
@@ -2681,28 +2681,28 @@
         <v>26.4</v>
       </c>
       <c r="M17">
-        <v>0.71790675</v>
+        <v>0.7657672000000001</v>
       </c>
       <c r="N17">
-        <v>25.68209325</v>
+        <v>25.6342328</v>
       </c>
       <c r="O17">
-        <v>6.420523312499999</v>
+        <v>6.4085582</v>
       </c>
       <c r="P17">
-        <v>19.2615699375</v>
+        <v>19.2256746</v>
       </c>
       <c r="Q17">
-        <v>21.7615699375</v>
+        <v>21.7256746</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.1174408346974871</v>
+        <v>0.1181054064479276</v>
       </c>
       <c r="T17">
-        <v>1.042461436550622</v>
+        <v>1.052131765275582</v>
       </c>
       <c r="U17">
         <v>0.0503</v>
@@ -2719,7 +2719,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>36.77357818407474</v>
+        <v>34.47522954757007</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2727,22 +2727,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.1052445414162591</v>
+        <v>0.1050056233396543</v>
       </c>
       <c r="C18">
-        <v>80.80232627881151</v>
+        <v>79.90942303913613</v>
       </c>
       <c r="D18">
-        <v>59.72632627881151</v>
+        <v>59.78492303913614</v>
       </c>
       <c r="E18">
-        <v>10.774</v>
+        <v>11.7255</v>
       </c>
       <c r="F18">
-        <v>15.224</v>
+        <v>16.1755</v>
       </c>
       <c r="G18">
         <v>36.3</v>
@@ -2763,28 +2763,28 @@
         <v>26.4</v>
       </c>
       <c r="M18">
-        <v>0.7657672000000001</v>
+        <v>0.8136276500000001</v>
       </c>
       <c r="N18">
-        <v>25.6342328</v>
+        <v>25.58637235</v>
       </c>
       <c r="O18">
-        <v>6.4085582</v>
+        <v>6.396593087499999</v>
       </c>
       <c r="P18">
-        <v>19.2256746</v>
+        <v>19.1897792625</v>
       </c>
       <c r="Q18">
-        <v>21.7256746</v>
+        <v>21.6897792625</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.1181054064479276</v>
+        <v>0.1187859919754871</v>
       </c>
       <c r="T18">
-        <v>1.052131765275582</v>
+        <v>1.062035113969817</v>
       </c>
       <c r="U18">
         <v>0.0503</v>
@@ -2801,7 +2801,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>34.47522954757007</v>
+        <v>32.44727486830124</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2809,22 +2809,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.1050056233396543</v>
+        <v>0.1047667052630495</v>
       </c>
       <c r="C19">
-        <v>79.90942303913613</v>
+        <v>79.01663488948842</v>
       </c>
       <c r="D19">
-        <v>59.78492303913614</v>
+        <v>59.84363488948842</v>
       </c>
       <c r="E19">
-        <v>11.7255</v>
+        <v>12.677</v>
       </c>
       <c r="F19">
-        <v>16.1755</v>
+        <v>17.127</v>
       </c>
       <c r="G19">
         <v>36.3</v>
@@ -2845,28 +2845,28 @@
         <v>26.4</v>
       </c>
       <c r="M19">
-        <v>0.8136276500000001</v>
+        <v>0.8614881000000001</v>
       </c>
       <c r="N19">
-        <v>25.58637235</v>
+        <v>25.5385119</v>
       </c>
       <c r="O19">
-        <v>6.396593087499999</v>
+        <v>6.384627975</v>
       </c>
       <c r="P19">
-        <v>19.1897792625</v>
+        <v>19.153883925</v>
       </c>
       <c r="Q19">
-        <v>21.6897792625</v>
+        <v>21.653883925</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.1187859919754871</v>
+        <v>0.1194831771500603</v>
       </c>
       <c r="T19">
-        <v>1.062035113969817</v>
+        <v>1.072180007754156</v>
       </c>
       <c r="U19">
         <v>0.0503</v>
@@ -2883,7 +2883,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>32.44727486830124</v>
+        <v>30.64464848672895</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2891,22 +2891,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.1047667052630495</v>
+        <v>0.1045277871864446</v>
       </c>
       <c r="C20">
-        <v>79.01663488948843</v>
+        <v>78.12396216927455</v>
       </c>
       <c r="D20">
-        <v>59.84363488948842</v>
+        <v>59.90246216927456</v>
       </c>
       <c r="E20">
-        <v>12.677</v>
+        <v>13.6285</v>
       </c>
       <c r="F20">
-        <v>17.127</v>
+        <v>18.0785</v>
       </c>
       <c r="G20">
         <v>36.3</v>
@@ -2927,28 +2927,28 @@
         <v>26.4</v>
       </c>
       <c r="M20">
-        <v>0.8614880999999999</v>
+        <v>0.90934855</v>
       </c>
       <c r="N20">
-        <v>25.5385119</v>
+        <v>25.49065145</v>
       </c>
       <c r="O20">
-        <v>6.384627975</v>
+        <v>6.372662862499999</v>
       </c>
       <c r="P20">
-        <v>19.153883925</v>
+        <v>19.1179885875</v>
       </c>
       <c r="Q20">
-        <v>21.653883925</v>
+        <v>21.6179885875</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.1194831771500603</v>
+        <v>0.1201975767733884</v>
       </c>
       <c r="T20">
-        <v>1.072180007754156</v>
+        <v>1.082575392743047</v>
       </c>
       <c r="U20">
         <v>0.0503</v>
@@ -2965,7 +2965,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>30.64464848672896</v>
+        <v>29.03177225058532</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2973,22 +2973,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.1045277871864446</v>
+        <v>0.1042888691098398</v>
       </c>
       <c r="C21">
-        <v>78.12396216927455</v>
+        <v>77.23140521923661</v>
       </c>
       <c r="D21">
-        <v>59.90246216927456</v>
+        <v>59.96140521923661</v>
       </c>
       <c r="E21">
-        <v>13.6285</v>
+        <v>14.58</v>
       </c>
       <c r="F21">
-        <v>18.0785</v>
+        <v>19.03</v>
       </c>
       <c r="G21">
         <v>36.3</v>
@@ -3009,28 +3009,28 @@
         <v>26.4</v>
       </c>
       <c r="M21">
-        <v>0.90934855</v>
+        <v>0.957209</v>
       </c>
       <c r="N21">
-        <v>25.49065145</v>
+        <v>25.442791</v>
       </c>
       <c r="O21">
-        <v>6.372662862499999</v>
+        <v>6.36069775</v>
       </c>
       <c r="P21">
-        <v>19.1179885875</v>
+        <v>19.08209325</v>
       </c>
       <c r="Q21">
-        <v>21.6179885875</v>
+        <v>21.58209325</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.1201975767733884</v>
+        <v>0.1209298363872997</v>
       </c>
       <c r="T21">
-        <v>1.082575392743047</v>
+        <v>1.093230662356659</v>
       </c>
       <c r="U21">
         <v>0.0503</v>
@@ -3047,7 +3047,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>29.03177225058532</v>
+        <v>27.58018363805606</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3055,22 +3055,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.1042888691098398</v>
+        <v>0.104049951033235</v>
       </c>
       <c r="C22">
-        <v>77.23140521923661</v>
+        <v>76.33896438145911</v>
       </c>
       <c r="D22">
-        <v>59.96140521923661</v>
+        <v>60.02046438145911</v>
       </c>
       <c r="E22">
-        <v>14.58</v>
+        <v>15.5315</v>
       </c>
       <c r="F22">
-        <v>19.03</v>
+        <v>19.9815</v>
       </c>
       <c r="G22">
         <v>36.3</v>
@@ -3091,28 +3091,28 @@
         <v>26.4</v>
       </c>
       <c r="M22">
-        <v>0.957209</v>
+        <v>1.00506945</v>
       </c>
       <c r="N22">
-        <v>25.442791</v>
+        <v>25.39493055</v>
       </c>
       <c r="O22">
-        <v>6.36069775</v>
+        <v>6.348732637499999</v>
       </c>
       <c r="P22">
-        <v>19.08209325</v>
+        <v>19.0461979125</v>
       </c>
       <c r="Q22">
-        <v>21.58209325</v>
+        <v>21.5461979125</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.1209298363872997</v>
+        <v>0.1216806342192847</v>
       </c>
       <c r="T22">
-        <v>1.093230662356659</v>
+        <v>1.104155685631376</v>
       </c>
       <c r="U22">
         <v>0.0503</v>
@@ -3129,7 +3129,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>27.58018363805606</v>
+        <v>26.26684156005338</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3137,22 +3137,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.1040499510332349</v>
+        <v>0.1038110329566301</v>
       </c>
       <c r="C23">
-        <v>76.33896438145912</v>
+        <v>75.44663999937566</v>
       </c>
       <c r="D23">
-        <v>60.02046438145911</v>
+        <v>60.07963999937565</v>
       </c>
       <c r="E23">
-        <v>15.5315</v>
+        <v>16.483</v>
       </c>
       <c r="F23">
-        <v>19.9815</v>
+        <v>20.933</v>
       </c>
       <c r="G23">
         <v>36.3</v>
@@ -3173,28 +3173,28 @@
         <v>26.4</v>
       </c>
       <c r="M23">
-        <v>1.00506945</v>
+        <v>1.0529299</v>
       </c>
       <c r="N23">
-        <v>25.39493055</v>
+        <v>25.3470701</v>
       </c>
       <c r="O23">
-        <v>6.348732637499999</v>
+        <v>6.336767525</v>
       </c>
       <c r="P23">
-        <v>19.0461979125</v>
+        <v>19.010302575</v>
       </c>
       <c r="Q23">
-        <v>21.5461979125</v>
+        <v>21.510302575</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.1216806342192847</v>
+        <v>0.1224506832777309</v>
       </c>
       <c r="T23">
-        <v>1.104155685631376</v>
+        <v>1.115360837708008</v>
       </c>
       <c r="U23">
         <v>0.0503</v>
@@ -3211,7 +3211,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>26.26684156005339</v>
+        <v>25.0728942164146</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3219,22 +3219,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.1038110329566301</v>
+        <v>0.1035721148800252</v>
       </c>
       <c r="C24">
-        <v>75.44663999937566</v>
+        <v>74.55443241777556</v>
       </c>
       <c r="D24">
-        <v>60.07963999937565</v>
+        <v>60.13893241777557</v>
       </c>
       <c r="E24">
-        <v>16.483</v>
+        <v>17.4345</v>
       </c>
       <c r="F24">
-        <v>20.933</v>
+        <v>21.8845</v>
       </c>
       <c r="G24">
         <v>36.3</v>
@@ -3255,28 +3255,28 @@
         <v>26.4</v>
       </c>
       <c r="M24">
-        <v>1.0529299</v>
+        <v>1.10079035</v>
       </c>
       <c r="N24">
-        <v>25.3470701</v>
+        <v>25.29920965</v>
       </c>
       <c r="O24">
-        <v>6.336767525</v>
+        <v>6.3248024125</v>
       </c>
       <c r="P24">
-        <v>19.010302575</v>
+        <v>18.9744072375</v>
       </c>
       <c r="Q24">
-        <v>21.510302575</v>
+        <v>21.4744072375</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.1224506832777309</v>
+        <v>0.1232407336104224</v>
       </c>
       <c r="T24">
-        <v>1.115360837708008</v>
+        <v>1.126857032695722</v>
       </c>
       <c r="U24">
         <v>0.0503</v>
@@ -3293,7 +3293,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>25.0728942164146</v>
+        <v>23.98276838091831</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3301,22 +3301,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.1035721148800252</v>
+        <v>0.1033331968034204</v>
       </c>
       <c r="C25">
-        <v>74.55443241777556</v>
+        <v>73.66234198281062</v>
       </c>
       <c r="D25">
-        <v>60.13893241777557</v>
+        <v>60.19834198281062</v>
       </c>
       <c r="E25">
-        <v>17.4345</v>
+        <v>18.386</v>
       </c>
       <c r="F25">
-        <v>21.8845</v>
+        <v>22.836</v>
       </c>
       <c r="G25">
         <v>36.3</v>
@@ -3337,28 +3337,28 @@
         <v>26.4</v>
       </c>
       <c r="M25">
-        <v>1.10079035</v>
+        <v>1.1486508</v>
       </c>
       <c r="N25">
-        <v>25.29920965</v>
+        <v>25.2513492</v>
       </c>
       <c r="O25">
-        <v>6.3248024125</v>
+        <v>6.3128373</v>
       </c>
       <c r="P25">
-        <v>18.9744072375</v>
+        <v>18.9385119</v>
       </c>
       <c r="Q25">
-        <v>21.4744072375</v>
+        <v>21.4385119</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.1232407336104224</v>
+        <v>0.1240515747413427</v>
       </c>
       <c r="T25">
-        <v>1.126857032695722</v>
+        <v>1.138655759130482</v>
       </c>
       <c r="U25">
         <v>0.0503</v>
@@ -3375,7 +3375,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>23.98276838091831</v>
+        <v>22.98348636504672</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3383,22 +3383,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.1033331968034204</v>
+        <v>0.1030942787268156</v>
       </c>
       <c r="C26">
-        <v>73.66234198281063</v>
+        <v>72.77036904200176</v>
       </c>
       <c r="D26">
-        <v>60.19834198281063</v>
+        <v>60.25786904200177</v>
       </c>
       <c r="E26">
-        <v>18.386</v>
+        <v>19.3375</v>
       </c>
       <c r="F26">
-        <v>22.836</v>
+        <v>23.7875</v>
       </c>
       <c r="G26">
         <v>36.3</v>
@@ -3419,28 +3419,28 @@
         <v>26.4</v>
       </c>
       <c r="M26">
-        <v>1.1486508</v>
+        <v>1.19651125</v>
       </c>
       <c r="N26">
-        <v>25.2513492</v>
+        <v>25.20348875</v>
       </c>
       <c r="O26">
-        <v>6.3128373</v>
+        <v>6.3008721875</v>
       </c>
       <c r="P26">
-        <v>18.9385119</v>
+        <v>18.9026165625</v>
       </c>
       <c r="Q26">
-        <v>21.4385119</v>
+        <v>21.4026165625</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.1240515747413427</v>
+        <v>0.1248840383024208</v>
       </c>
       <c r="T26">
-        <v>1.138655759130482</v>
+        <v>1.150769118270168</v>
       </c>
       <c r="U26">
         <v>0.0503</v>
@@ -3457,7 +3457,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>22.98348636504672</v>
+        <v>22.06414691044484</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3465,22 +3465,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.1030942787268156</v>
+        <v>0.1028553606502107</v>
       </c>
       <c r="C27">
-        <v>72.77036904200176</v>
+        <v>71.87851394424587</v>
       </c>
       <c r="D27">
-        <v>60.25786904200177</v>
+        <v>60.31751394424587</v>
       </c>
       <c r="E27">
-        <v>19.3375</v>
+        <v>20.289</v>
       </c>
       <c r="F27">
-        <v>23.7875</v>
+        <v>24.739</v>
       </c>
       <c r="G27">
         <v>36.3</v>
@@ -3501,28 +3501,28 @@
         <v>26.4</v>
       </c>
       <c r="M27">
-        <v>1.19651125</v>
+        <v>1.2443717</v>
       </c>
       <c r="N27">
-        <v>25.20348875</v>
+        <v>25.1556283</v>
       </c>
       <c r="O27">
-        <v>6.3008721875</v>
+        <v>6.288907075</v>
       </c>
       <c r="P27">
-        <v>18.9026165625</v>
+        <v>18.866721225</v>
       </c>
       <c r="Q27">
-        <v>21.4026165625</v>
+        <v>21.366721225</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.1248840383024208</v>
+        <v>0.1257390008786632</v>
       </c>
       <c r="T27">
-        <v>1.150769118270168</v>
+        <v>1.16320986549471</v>
       </c>
       <c r="U27">
         <v>0.0503</v>
@@ -3539,7 +3539,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>22.06414691044484</v>
+        <v>21.21552587542773</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3547,22 +3547,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.1028553606502107</v>
+        <v>0.1026164425736059</v>
       </c>
       <c r="C28">
-        <v>71.87851394424587</v>
+        <v>70.98677703982257</v>
       </c>
       <c r="D28">
-        <v>60.31751394424587</v>
+        <v>60.37727703982257</v>
       </c>
       <c r="E28">
-        <v>20.289</v>
+        <v>21.2405</v>
       </c>
       <c r="F28">
-        <v>24.739</v>
+        <v>25.6905</v>
       </c>
       <c r="G28">
         <v>36.3</v>
@@ -3583,28 +3583,28 @@
         <v>26.4</v>
       </c>
       <c r="M28">
-        <v>1.2443717</v>
+        <v>1.29223215</v>
       </c>
       <c r="N28">
-        <v>25.1556283</v>
+        <v>25.10776785</v>
       </c>
       <c r="O28">
-        <v>6.288907075</v>
+        <v>6.2769419625</v>
       </c>
       <c r="P28">
-        <v>18.866721225</v>
+        <v>18.8308258875</v>
       </c>
       <c r="Q28">
-        <v>21.366721225</v>
+        <v>21.3308258875</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.1257390008786632</v>
+        <v>0.1266173870871314</v>
       </c>
       <c r="T28">
-        <v>1.16320986549471</v>
+        <v>1.175991455108966</v>
       </c>
       <c r="U28">
         <v>0.0503</v>
@@ -3621,7 +3621,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>21.21552587542773</v>
+        <v>20.4297656578193</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3629,22 +3629,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.1026164425736059</v>
+        <v>0.1023775244970011</v>
       </c>
       <c r="C29">
-        <v>70.98677703982257</v>
+        <v>70.09515868040111</v>
       </c>
       <c r="D29">
-        <v>60.37727703982257</v>
+        <v>60.4371586804011</v>
       </c>
       <c r="E29">
-        <v>21.2405</v>
+        <v>22.192</v>
       </c>
       <c r="F29">
-        <v>25.6905</v>
+        <v>26.642</v>
       </c>
       <c r="G29">
         <v>36.3</v>
@@ -3665,28 +3665,28 @@
         <v>26.4</v>
       </c>
       <c r="M29">
-        <v>1.29223215</v>
+        <v>1.3400926</v>
       </c>
       <c r="N29">
-        <v>25.10776785</v>
+        <v>25.0599074</v>
       </c>
       <c r="O29">
-        <v>6.2769419625</v>
+        <v>6.26497685</v>
       </c>
       <c r="P29">
-        <v>18.8308258875</v>
+        <v>18.79493055</v>
       </c>
       <c r="Q29">
-        <v>21.3308258875</v>
+        <v>21.29493055</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.1266173870871314</v>
+        <v>0.1275201729125015</v>
       </c>
       <c r="T29">
-        <v>1.175991455108966</v>
+        <v>1.189128088879173</v>
       </c>
       <c r="U29">
         <v>0.0503</v>
@@ -3703,7 +3703,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>20.4297656578193</v>
+        <v>19.70013117004004</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3711,22 +3711,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.1023775244970011</v>
+        <v>0.1021386064203962</v>
       </c>
       <c r="C30">
-        <v>70.09515868040111</v>
+        <v>69.20365921904727</v>
       </c>
       <c r="D30">
-        <v>60.4371586804011</v>
+        <v>60.49715921904728</v>
       </c>
       <c r="E30">
-        <v>22.192</v>
+        <v>23.14350000000001</v>
       </c>
       <c r="F30">
-        <v>26.642</v>
+        <v>27.59350000000001</v>
       </c>
       <c r="G30">
         <v>36.3</v>
@@ -3747,28 +3747,28 @@
         <v>26.4</v>
       </c>
       <c r="M30">
-        <v>1.3400926</v>
+        <v>1.38795305</v>
       </c>
       <c r="N30">
-        <v>25.0599074</v>
+        <v>25.01204695</v>
       </c>
       <c r="O30">
-        <v>6.26497685</v>
+        <v>6.2530117375</v>
       </c>
       <c r="P30">
-        <v>18.79493055</v>
+        <v>18.7590352125</v>
       </c>
       <c r="Q30">
-        <v>21.29493055</v>
+        <v>21.2590352125</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.1275201729125015</v>
+        <v>0.1284483893245017</v>
       </c>
       <c r="T30">
-        <v>1.189128088879173</v>
+        <v>1.202634768671076</v>
       </c>
       <c r="U30">
         <v>0.0503</v>
@@ -3785,7 +3785,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>19.70013117004004</v>
+        <v>19.02081630210762</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3793,22 +3793,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.1021386064203962</v>
+        <v>0.1018996883437914</v>
       </c>
       <c r="C31">
-        <v>69.20365921904727</v>
+        <v>68.31227901023028</v>
       </c>
       <c r="D31">
-        <v>60.49715921904728</v>
+        <v>60.5572790102303</v>
       </c>
       <c r="E31">
-        <v>23.1435</v>
+        <v>24.095</v>
       </c>
       <c r="F31">
-        <v>27.5935</v>
+        <v>28.545</v>
       </c>
       <c r="G31">
         <v>36.3</v>
@@ -3829,28 +3829,28 @@
         <v>26.4</v>
       </c>
       <c r="M31">
-        <v>1.38795305</v>
+        <v>1.4358135</v>
       </c>
       <c r="N31">
-        <v>25.01204695</v>
+        <v>24.9641865</v>
       </c>
       <c r="O31">
-        <v>6.2530117375</v>
+        <v>6.241046624999999</v>
       </c>
       <c r="P31">
-        <v>18.7590352125</v>
+        <v>18.723139875</v>
       </c>
       <c r="Q31">
-        <v>21.2590352125</v>
+        <v>21.223139875</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.1284483893245017</v>
+        <v>0.1294031262054162</v>
       </c>
       <c r="T31">
-        <v>1.202634768671076</v>
+        <v>1.216527353599891</v>
       </c>
       <c r="U31">
         <v>0.0503</v>
@@ -3867,7 +3867,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>19.02081630210763</v>
+        <v>18.38678909203737</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3875,22 +3875,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.1018996883437914</v>
+        <v>0.1016607702671865</v>
       </c>
       <c r="C32">
-        <v>68.31227901023028</v>
+        <v>67.4210184098298</v>
       </c>
       <c r="D32">
-        <v>60.5572790102303</v>
+        <v>60.61751840982979</v>
       </c>
       <c r="E32">
-        <v>24.095</v>
+        <v>25.0465</v>
       </c>
       <c r="F32">
-        <v>28.545</v>
+        <v>29.4965</v>
       </c>
       <c r="G32">
         <v>36.3</v>
@@ -3911,28 +3911,28 @@
         <v>26.4</v>
       </c>
       <c r="M32">
-        <v>1.4358135</v>
+        <v>1.48367395</v>
       </c>
       <c r="N32">
-        <v>24.9641865</v>
+        <v>24.91632605</v>
       </c>
       <c r="O32">
-        <v>6.241046624999999</v>
+        <v>6.2290815125</v>
       </c>
       <c r="P32">
-        <v>18.723139875</v>
+        <v>18.6872445375</v>
       </c>
       <c r="Q32">
-        <v>21.223139875</v>
+        <v>21.1872445375</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.1294031262054162</v>
+        <v>0.1303855366191109</v>
       </c>
       <c r="T32">
-        <v>1.216527353599891</v>
+        <v>1.230822622149831</v>
       </c>
       <c r="U32">
         <v>0.0503</v>
@@ -3949,7 +3949,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>18.38678909203737</v>
+        <v>17.79366686326197</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3957,22 +3957,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.1016607702671865</v>
+        <v>0.1014218521905817</v>
       </c>
       <c r="C33">
-        <v>67.4210184098298</v>
+        <v>66.52987777514289</v>
       </c>
       <c r="D33">
-        <v>60.61751840982979</v>
+        <v>60.6778777751429</v>
       </c>
       <c r="E33">
-        <v>25.0465</v>
+        <v>25.998</v>
       </c>
       <c r="F33">
-        <v>29.4965</v>
+        <v>30.448</v>
       </c>
       <c r="G33">
         <v>36.3</v>
@@ -3993,28 +3993,28 @@
         <v>26.4</v>
       </c>
       <c r="M33">
-        <v>1.48367395</v>
+        <v>1.5315344</v>
       </c>
       <c r="N33">
-        <v>24.91632605</v>
+        <v>24.8684656</v>
       </c>
       <c r="O33">
-        <v>6.2290815125</v>
+        <v>6.217116399999999</v>
       </c>
       <c r="P33">
-        <v>18.6872445375</v>
+        <v>18.6513492</v>
       </c>
       <c r="Q33">
-        <v>21.1872445375</v>
+        <v>21.1513492</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.1303855366191109</v>
+        <v>0.1313968414567378</v>
       </c>
       <c r="T33">
-        <v>1.230822622149831</v>
+        <v>1.24553833977477</v>
       </c>
       <c r="U33">
         <v>0.0503</v>
@@ -4031,7 +4031,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>17.79366686326197</v>
+        <v>17.23761477378503</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4039,22 +4039,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.1014218521905817</v>
+        <v>0.1011829341139768</v>
       </c>
       <c r="C34">
-        <v>66.52987777514289</v>
+        <v>65.63885746489126</v>
       </c>
       <c r="D34">
-        <v>60.6778777751429</v>
+        <v>60.73835746489127</v>
       </c>
       <c r="E34">
-        <v>25.998</v>
+        <v>26.9495</v>
       </c>
       <c r="F34">
-        <v>30.448</v>
+        <v>31.3995</v>
       </c>
       <c r="G34">
         <v>36.3</v>
@@ -4075,28 +4075,28 @@
         <v>26.4</v>
       </c>
       <c r="M34">
-        <v>1.5315344</v>
+        <v>1.57939485</v>
       </c>
       <c r="N34">
-        <v>24.8684656</v>
+        <v>24.82060515</v>
       </c>
       <c r="O34">
-        <v>6.217116399999999</v>
+        <v>6.2051512875</v>
       </c>
       <c r="P34">
-        <v>18.6513492</v>
+        <v>18.6154538625</v>
       </c>
       <c r="Q34">
-        <v>21.1513492</v>
+        <v>21.1154538625</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1313968414567378</v>
+        <v>0.1324383344984729</v>
       </c>
       <c r="T34">
-        <v>1.24553833977477</v>
+        <v>1.260693332552691</v>
       </c>
       <c r="U34">
         <v>0.0503</v>
@@ -4113,7 +4113,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>17.23761477378503</v>
+        <v>16.71526281094306</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4121,22 +4121,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.1011829341139768</v>
+        <v>0.100944016037372</v>
       </c>
       <c r="C35">
-        <v>65.63885746489126</v>
+        <v>64.74795783922812</v>
       </c>
       <c r="D35">
-        <v>60.73835746489127</v>
+        <v>60.79895783922813</v>
       </c>
       <c r="E35">
-        <v>26.9495</v>
+        <v>27.90100000000001</v>
       </c>
       <c r="F35">
-        <v>31.3995</v>
+        <v>32.35100000000001</v>
       </c>
       <c r="G35">
         <v>36.3</v>
@@ -4157,28 +4157,28 @@
         <v>26.4</v>
       </c>
       <c r="M35">
-        <v>1.57939485</v>
+        <v>1.6272553</v>
       </c>
       <c r="N35">
-        <v>24.82060515</v>
+        <v>24.7727447</v>
       </c>
       <c r="O35">
-        <v>6.2051512875</v>
+        <v>6.193186174999999</v>
       </c>
       <c r="P35">
-        <v>18.6154538625</v>
+        <v>18.579558525</v>
       </c>
       <c r="Q35">
-        <v>21.1154538625</v>
+        <v>21.079558525</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1324383344984729</v>
+        <v>0.1335113879354121</v>
       </c>
       <c r="T35">
-        <v>1.260693332552691</v>
+        <v>1.276307567536004</v>
       </c>
       <c r="U35">
         <v>0.0503</v>
@@ -4195,7 +4195,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>16.71526281094306</v>
+        <v>16.22363743415062</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4203,22 +4203,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.100944016037372</v>
+        <v>0.1007050979607672</v>
       </c>
       <c r="C36">
-        <v>64.74795783922812</v>
+        <v>63.85717925974553</v>
       </c>
       <c r="D36">
-        <v>60.79895783922813</v>
+        <v>60.85967925974553</v>
       </c>
       <c r="E36">
-        <v>27.90100000000001</v>
+        <v>28.8525</v>
       </c>
       <c r="F36">
-        <v>32.35100000000001</v>
+        <v>33.3025</v>
       </c>
       <c r="G36">
         <v>36.3</v>
@@ -4239,28 +4239,28 @@
         <v>26.4</v>
       </c>
       <c r="M36">
-        <v>1.6272553</v>
+        <v>1.67511575</v>
       </c>
       <c r="N36">
-        <v>24.7727447</v>
+        <v>24.72488425</v>
       </c>
       <c r="O36">
-        <v>6.193186174999999</v>
+        <v>6.1812210625</v>
       </c>
       <c r="P36">
-        <v>18.579558525</v>
+        <v>18.5436631875</v>
       </c>
       <c r="Q36">
-        <v>21.079558525</v>
+        <v>21.0436631875</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1335113879354121</v>
+        <v>0.1346174584011803</v>
       </c>
       <c r="T36">
-        <v>1.276307567536004</v>
+        <v>1.292402240518804</v>
       </c>
       <c r="U36">
         <v>0.0503</v>
@@ -4277,7 +4277,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>16.22363743415062</v>
+        <v>15.76010493603203</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4285,22 +4285,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.1007050979607672</v>
+        <v>0.1004661798841623</v>
       </c>
       <c r="C37">
-        <v>63.85717925974553</v>
+        <v>62.96652208948147</v>
       </c>
       <c r="D37">
-        <v>60.85967925974553</v>
+        <v>60.92052208948149</v>
       </c>
       <c r="E37">
-        <v>28.8525</v>
+        <v>29.80400000000001</v>
       </c>
       <c r="F37">
-        <v>33.3025</v>
+        <v>34.254</v>
       </c>
       <c r="G37">
         <v>36.3</v>
@@ -4321,28 +4321,28 @@
         <v>26.4</v>
       </c>
       <c r="M37">
-        <v>1.67511575</v>
+        <v>1.7229762</v>
       </c>
       <c r="N37">
-        <v>24.72488425</v>
+        <v>24.6770238</v>
       </c>
       <c r="O37">
-        <v>6.1812210625</v>
+        <v>6.169255949999999</v>
       </c>
       <c r="P37">
-        <v>18.5436631875</v>
+        <v>18.50776785</v>
       </c>
       <c r="Q37">
-        <v>21.0436631875</v>
+        <v>21.00776785</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1346174584011803</v>
+        <v>0.1357580935690036</v>
       </c>
       <c r="T37">
-        <v>1.292402240518804</v>
+        <v>1.308999872032315</v>
       </c>
       <c r="U37">
         <v>0.0503</v>
@@ -4359,7 +4359,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>15.76010493603203</v>
+        <v>15.32232424336447</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4367,22 +4367,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.1004661798841623</v>
+        <v>0.1002272618075575</v>
       </c>
       <c r="C38">
-        <v>62.96652208948148</v>
+        <v>62.07598669292717</v>
       </c>
       <c r="D38">
-        <v>60.92052208948147</v>
+        <v>60.98148669292718</v>
       </c>
       <c r="E38">
-        <v>29.804</v>
+        <v>30.7555</v>
       </c>
       <c r="F38">
-        <v>34.254</v>
+        <v>35.2055</v>
       </c>
       <c r="G38">
         <v>36.3</v>
@@ -4403,28 +4403,28 @@
         <v>26.4</v>
       </c>
       <c r="M38">
-        <v>1.7229762</v>
+        <v>1.77083665</v>
       </c>
       <c r="N38">
-        <v>24.6770238</v>
+        <v>24.62916335</v>
       </c>
       <c r="O38">
-        <v>6.16925595</v>
+        <v>6.1572908375</v>
       </c>
       <c r="P38">
-        <v>18.50776785</v>
+        <v>18.4718725125</v>
       </c>
       <c r="Q38">
-        <v>21.00776785</v>
+        <v>20.9718725125</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1357580935690036</v>
+        <v>0.1369349393770754</v>
       </c>
       <c r="T38">
-        <v>1.308999872032315</v>
+        <v>1.326124412482764</v>
       </c>
       <c r="U38">
         <v>0.0503</v>
@@ -4441,7 +4441,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>15.32232424336448</v>
+        <v>14.90820737192219</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4449,22 +4449,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.1002272618075575</v>
+        <v>0.09998834373095264</v>
       </c>
       <c r="C39">
-        <v>62.07598669292717</v>
+        <v>61.1855734360343</v>
       </c>
       <c r="D39">
-        <v>60.98148669292718</v>
+        <v>61.0425734360343</v>
       </c>
       <c r="E39">
-        <v>30.7555</v>
+        <v>31.707</v>
       </c>
       <c r="F39">
-        <v>35.2055</v>
+        <v>36.157</v>
       </c>
       <c r="G39">
         <v>36.3</v>
@@ -4485,28 +4485,28 @@
         <v>26.4</v>
       </c>
       <c r="M39">
-        <v>1.77083665</v>
+        <v>1.8186971</v>
       </c>
       <c r="N39">
-        <v>24.62916335</v>
+        <v>24.5813029</v>
       </c>
       <c r="O39">
-        <v>6.1572908375</v>
+        <v>6.145325724999999</v>
       </c>
       <c r="P39">
-        <v>18.4718725125</v>
+        <v>18.435977175</v>
       </c>
       <c r="Q39">
-        <v>20.9718725125</v>
+        <v>20.935977175</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1369349393770754</v>
+        <v>0.1381497479531494</v>
       </c>
       <c r="T39">
-        <v>1.326124412482764</v>
+        <v>1.343801357463873</v>
       </c>
       <c r="U39">
         <v>0.0503</v>
@@ -4523,7 +4523,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>14.90820737192219</v>
+        <v>14.51588612529266</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4531,22 +4531,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.09998834373095264</v>
+        <v>0.0997494256543478</v>
       </c>
       <c r="C40">
-        <v>61.1855734360343</v>
+        <v>60.29528268622235</v>
       </c>
       <c r="D40">
-        <v>61.0425734360343</v>
+        <v>61.10378268622236</v>
       </c>
       <c r="E40">
-        <v>31.707</v>
+        <v>32.6585</v>
       </c>
       <c r="F40">
-        <v>36.157</v>
+        <v>37.10850000000001</v>
       </c>
       <c r="G40">
         <v>36.3</v>
@@ -4567,28 +4567,28 @@
         <v>26.4</v>
       </c>
       <c r="M40">
-        <v>1.8186971</v>
+        <v>1.86655755</v>
       </c>
       <c r="N40">
-        <v>24.5813029</v>
+        <v>24.53344245</v>
       </c>
       <c r="O40">
-        <v>6.145325724999999</v>
+        <v>6.1333606125</v>
       </c>
       <c r="P40">
-        <v>18.435977175</v>
+        <v>18.4000818375</v>
       </c>
       <c r="Q40">
-        <v>20.935977175</v>
+        <v>20.9000818375</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1381497479531494</v>
+        <v>0.139404386318603</v>
       </c>
       <c r="T40">
-        <v>1.343801357463873</v>
+        <v>1.362057874411575</v>
       </c>
       <c r="U40">
         <v>0.0503</v>
@@ -4605,7 +4605,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>14.51588612529266</v>
+        <v>14.14368391695182</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4613,22 +4613,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.0997494256543478</v>
+        <v>0.09951050757774296</v>
       </c>
       <c r="C41">
-        <v>60.29528268622235</v>
+        <v>59.405114812386</v>
       </c>
       <c r="D41">
-        <v>61.10378268622236</v>
+        <v>61.16511481238601</v>
       </c>
       <c r="E41">
-        <v>32.6585</v>
+        <v>33.61</v>
       </c>
       <c r="F41">
-        <v>37.10850000000001</v>
+        <v>38.06</v>
       </c>
       <c r="G41">
         <v>36.3</v>
@@ -4649,28 +4649,28 @@
         <v>26.4</v>
       </c>
       <c r="M41">
-        <v>1.86655755</v>
+        <v>1.914418</v>
       </c>
       <c r="N41">
-        <v>24.53344245</v>
+        <v>24.485582</v>
       </c>
       <c r="O41">
-        <v>6.1333606125</v>
+        <v>6.121395499999999</v>
       </c>
       <c r="P41">
-        <v>18.4000818375</v>
+        <v>18.3641865</v>
       </c>
       <c r="Q41">
-        <v>20.9000818375</v>
+        <v>20.8641865</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.139404386318603</v>
+        <v>0.1407008459629049</v>
       </c>
       <c r="T41">
-        <v>1.362057874411575</v>
+        <v>1.380922941924201</v>
       </c>
       <c r="U41">
         <v>0.0503</v>
@@ -4687,7 +4687,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>14.14368391695182</v>
+        <v>13.79009181902803</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4695,22 +4695,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.09951050757774296</v>
+        <v>0.09927158950113811</v>
       </c>
       <c r="C42">
-        <v>59.405114812386</v>
+        <v>58.51507018490249</v>
       </c>
       <c r="D42">
-        <v>61.16511481238601</v>
+        <v>61.2265701849025</v>
       </c>
       <c r="E42">
-        <v>33.61</v>
+        <v>34.5615</v>
       </c>
       <c r="F42">
-        <v>38.06</v>
+        <v>39.01150000000001</v>
       </c>
       <c r="G42">
         <v>36.3</v>
@@ -4731,28 +4731,28 @@
         <v>26.4</v>
       </c>
       <c r="M42">
-        <v>1.914418</v>
+        <v>1.96227845</v>
       </c>
       <c r="N42">
-        <v>24.485582</v>
+        <v>24.43772155</v>
       </c>
       <c r="O42">
-        <v>6.121395499999999</v>
+        <v>6.1094303875</v>
       </c>
       <c r="P42">
-        <v>18.3641865</v>
+        <v>18.3282911625</v>
       </c>
       <c r="Q42">
-        <v>20.8641865</v>
+        <v>20.8282911625</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1407008459629049</v>
+        <v>0.1420412533917595</v>
       </c>
       <c r="T42">
-        <v>1.380922941924201</v>
+        <v>1.400427503250814</v>
       </c>
       <c r="U42">
         <v>0.0503</v>
@@ -4769,7 +4769,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>13.79009181902803</v>
+        <v>13.4537481161249</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4777,22 +4777,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.09927158950113811</v>
+        <v>0.09903267142453327</v>
       </c>
       <c r="C43">
-        <v>58.51507018490249</v>
+        <v>57.62514917563909</v>
       </c>
       <c r="D43">
-        <v>61.2265701849025</v>
+        <v>61.28814917563911</v>
       </c>
       <c r="E43">
-        <v>34.5615</v>
+        <v>35.51300000000001</v>
       </c>
       <c r="F43">
-        <v>39.01150000000001</v>
+        <v>39.96300000000001</v>
       </c>
       <c r="G43">
         <v>36.3</v>
@@ -4813,28 +4813,28 @@
         <v>26.4</v>
       </c>
       <c r="M43">
-        <v>1.96227845</v>
+        <v>2.0101389</v>
       </c>
       <c r="N43">
-        <v>24.43772155</v>
+        <v>24.3898611</v>
       </c>
       <c r="O43">
-        <v>6.1094303875</v>
+        <v>6.097465274999999</v>
       </c>
       <c r="P43">
-        <v>18.3282911625</v>
+        <v>18.292395825</v>
       </c>
       <c r="Q43">
-        <v>20.8282911625</v>
+        <v>20.792395825</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1420412533917595</v>
+        <v>0.1434278817664367</v>
       </c>
       <c r="T43">
-        <v>1.400427503250814</v>
+        <v>1.420604635657655</v>
       </c>
       <c r="U43">
         <v>0.0503</v>
@@ -4851,7 +4851,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>13.4537481161249</v>
+        <v>13.13342078002669</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4859,22 +4859,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.09903267142453329</v>
+        <v>0.09927750334792844</v>
       </c>
       <c r="C44">
-        <v>57.62514917563909</v>
+        <v>56.61054751329289</v>
       </c>
       <c r="D44">
-        <v>61.28814917563909</v>
+        <v>61.22504751329289</v>
       </c>
       <c r="E44">
-        <v>35.513</v>
+        <v>36.4645</v>
       </c>
       <c r="F44">
-        <v>39.963</v>
+        <v>40.9145</v>
       </c>
       <c r="G44">
         <v>36.3</v>
@@ -4895,45 +4895,45 @@
         <v>26.4</v>
       </c>
       <c r="M44">
-        <v>2.0101389</v>
+        <v>2.1193711</v>
       </c>
       <c r="N44">
-        <v>24.3898611</v>
+        <v>24.2806289</v>
       </c>
       <c r="O44">
-        <v>6.097465274999999</v>
+        <v>6.070157225</v>
       </c>
       <c r="P44">
-        <v>18.292395825</v>
+        <v>18.210471675</v>
       </c>
       <c r="Q44">
-        <v>20.792395825</v>
+        <v>20.710471675</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1434278817664367</v>
+        <v>0.1448631637682955</v>
       </c>
       <c r="T44">
-        <v>1.420604635657655</v>
+        <v>1.441489737622631</v>
       </c>
       <c r="U44">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V44">
         <v>0.25</v>
       </c>
       <c r="W44">
-        <v>0.03772499999999999</v>
+        <v>0.03885</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y44">
-        <v>13.13342078002669</v>
+        <v>12.45652542869911</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4941,22 +4941,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.09927750334792844</v>
+        <v>0.09904983527132361</v>
       </c>
       <c r="C45">
-        <v>56.61054751329289</v>
+        <v>55.71772121876209</v>
       </c>
       <c r="D45">
-        <v>61.22504751329289</v>
+        <v>61.2837212187621</v>
       </c>
       <c r="E45">
-        <v>36.4645</v>
+        <v>37.416</v>
       </c>
       <c r="F45">
-        <v>40.9145</v>
+        <v>41.866</v>
       </c>
       <c r="G45">
         <v>36.3</v>
@@ -4977,28 +4977,28 @@
         <v>26.4</v>
       </c>
       <c r="M45">
-        <v>2.1193711</v>
+        <v>2.1686588</v>
       </c>
       <c r="N45">
-        <v>24.2806289</v>
+        <v>24.2313412</v>
       </c>
       <c r="O45">
-        <v>6.070157225</v>
+        <v>6.0578353</v>
       </c>
       <c r="P45">
-        <v>18.210471675</v>
+        <v>18.1735059</v>
       </c>
       <c r="Q45">
-        <v>20.710471675</v>
+        <v>20.6735059</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1448631637682955</v>
+        <v>0.1463497058416493</v>
       </c>
       <c r="T45">
-        <v>1.441489737622631</v>
+        <v>1.463120736086356</v>
       </c>
       <c r="U45">
         <v>0.0518</v>
@@ -5015,7 +5015,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>12.45652542869911</v>
+        <v>12.17342257804686</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5023,22 +5023,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.09904983527132361</v>
+        <v>0.09882216719471874</v>
       </c>
       <c r="C46">
-        <v>55.71772121876209</v>
+        <v>54.82500748946932</v>
       </c>
       <c r="D46">
-        <v>61.2837212187621</v>
+        <v>61.34250748946933</v>
       </c>
       <c r="E46">
-        <v>37.416</v>
+        <v>38.3675</v>
       </c>
       <c r="F46">
-        <v>41.866</v>
+        <v>42.8175</v>
       </c>
       <c r="G46">
         <v>36.3</v>
@@ -5059,28 +5059,28 @@
         <v>26.4</v>
       </c>
       <c r="M46">
-        <v>2.1686588</v>
+        <v>2.2179465</v>
       </c>
       <c r="N46">
-        <v>24.2313412</v>
+        <v>24.1820535</v>
       </c>
       <c r="O46">
-        <v>6.0578353</v>
+        <v>6.045513375</v>
       </c>
       <c r="P46">
-        <v>18.1735059</v>
+        <v>18.136540125</v>
       </c>
       <c r="Q46">
-        <v>20.6735059</v>
+        <v>20.636540125</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1463497058416493</v>
+        <v>0.1478903039903977</v>
       </c>
       <c r="T46">
-        <v>1.463120736086356</v>
+        <v>1.485538316312398</v>
       </c>
       <c r="U46">
         <v>0.0518</v>
@@ -5097,7 +5097,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>12.17342257804686</v>
+        <v>11.90290207631248</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5105,22 +5105,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.09882216719471874</v>
+        <v>0.09859449911811391</v>
       </c>
       <c r="C47">
-        <v>54.82500748946932</v>
+        <v>53.93240664965944</v>
       </c>
       <c r="D47">
-        <v>61.34250748946933</v>
+        <v>61.40140664965946</v>
       </c>
       <c r="E47">
-        <v>38.3675</v>
+        <v>39.319</v>
       </c>
       <c r="F47">
-        <v>42.8175</v>
+        <v>43.76900000000001</v>
       </c>
       <c r="G47">
         <v>36.3</v>
@@ -5141,28 +5141,28 @@
         <v>26.4</v>
       </c>
       <c r="M47">
-        <v>2.2179465</v>
+        <v>2.2672342</v>
       </c>
       <c r="N47">
-        <v>24.1820535</v>
+        <v>24.1327658</v>
       </c>
       <c r="O47">
-        <v>6.045513375</v>
+        <v>6.033191449999999</v>
       </c>
       <c r="P47">
-        <v>18.136540125</v>
+        <v>18.09957435</v>
       </c>
       <c r="Q47">
-        <v>20.636540125</v>
+        <v>20.59957435</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1478903039903977</v>
+        <v>0.1494879613298406</v>
       </c>
       <c r="T47">
-        <v>1.485538316312398</v>
+        <v>1.508786177287553</v>
       </c>
       <c r="U47">
         <v>0.0518</v>
@@ -5179,7 +5179,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>11.90290207631248</v>
+        <v>11.64414333552308</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5187,22 +5187,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.09859449911811391</v>
+        <v>0.09836683104150906</v>
       </c>
       <c r="C48">
-        <v>53.93240664965944</v>
+        <v>53.0399190248239</v>
       </c>
       <c r="D48">
-        <v>61.40140664965946</v>
+        <v>61.46041902482391</v>
       </c>
       <c r="E48">
-        <v>39.319</v>
+        <v>40.27050000000001</v>
       </c>
       <c r="F48">
-        <v>43.76900000000001</v>
+        <v>44.72050000000001</v>
       </c>
       <c r="G48">
         <v>36.3</v>
@@ -5223,28 +5223,28 @@
         <v>26.4</v>
       </c>
       <c r="M48">
-        <v>2.2672342</v>
+        <v>2.316521900000001</v>
       </c>
       <c r="N48">
-        <v>24.1327658</v>
+        <v>24.0834781</v>
       </c>
       <c r="O48">
-        <v>6.033191449999999</v>
+        <v>6.020869524999999</v>
       </c>
       <c r="P48">
-        <v>18.09957435</v>
+        <v>18.062608575</v>
       </c>
       <c r="Q48">
-        <v>20.59957435</v>
+        <v>20.562608575</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1494879613298406</v>
+        <v>0.1511459076254888</v>
       </c>
       <c r="T48">
-        <v>1.508786177287553</v>
+        <v>1.532911316035355</v>
       </c>
       <c r="U48">
         <v>0.0518</v>
@@ -5261,7 +5261,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>11.64414333552308</v>
+        <v>11.39639560498003</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5269,22 +5269,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.09836683104150906</v>
+        <v>0.09813916296490421</v>
       </c>
       <c r="C49">
-        <v>53.0399190248239</v>
+        <v>52.14754494170653</v>
       </c>
       <c r="D49">
-        <v>61.46041902482391</v>
+        <v>61.51954494170654</v>
       </c>
       <c r="E49">
-        <v>40.27050000000001</v>
+        <v>41.222</v>
       </c>
       <c r="F49">
-        <v>44.72050000000001</v>
+        <v>45.672</v>
       </c>
       <c r="G49">
         <v>36.3</v>
@@ -5305,28 +5305,28 @@
         <v>26.4</v>
       </c>
       <c r="M49">
-        <v>2.316521900000001</v>
+        <v>2.3658096</v>
       </c>
       <c r="N49">
-        <v>24.0834781</v>
+        <v>24.0341904</v>
       </c>
       <c r="O49">
-        <v>6.020869524999999</v>
+        <v>6.0085476</v>
       </c>
       <c r="P49">
-        <v>18.062608575</v>
+        <v>18.0256428</v>
       </c>
       <c r="Q49">
-        <v>20.562608575</v>
+        <v>20.5256428</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1511459076254888</v>
+        <v>0.1528676210863543</v>
       </c>
       <c r="T49">
-        <v>1.532911316035355</v>
+        <v>1.557964344734996</v>
       </c>
       <c r="U49">
         <v>0.0518</v>
@@ -5343,7 +5343,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>11.39639560498003</v>
+        <v>11.15897069654295</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5351,22 +5351,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.09813916296490421</v>
+        <v>0.09791149488829938</v>
       </c>
       <c r="C50">
-        <v>52.14754494170653</v>
+        <v>51.25528472830985</v>
       </c>
       <c r="D50">
-        <v>61.51954494170654</v>
+        <v>61.57878472830986</v>
       </c>
       <c r="E50">
-        <v>41.222</v>
+        <v>42.1735</v>
       </c>
       <c r="F50">
-        <v>45.672</v>
+        <v>46.6235</v>
       </c>
       <c r="G50">
         <v>36.3</v>
@@ -5387,28 +5387,28 @@
         <v>26.4</v>
       </c>
       <c r="M50">
-        <v>2.3658096</v>
+        <v>2.4150973</v>
       </c>
       <c r="N50">
-        <v>24.0341904</v>
+        <v>23.9849027</v>
       </c>
       <c r="O50">
-        <v>6.0085476</v>
+        <v>5.996225675</v>
       </c>
       <c r="P50">
-        <v>18.0256428</v>
+        <v>17.988677025</v>
       </c>
       <c r="Q50">
-        <v>20.5256428</v>
+        <v>20.488677025</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1528676210863543</v>
+        <v>0.1546568527221557</v>
       </c>
       <c r="T50">
-        <v>1.557964344734996</v>
+        <v>1.583999845148348</v>
       </c>
       <c r="U50">
         <v>0.0518</v>
@@ -5425,7 +5425,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>11.15897069654295</v>
+        <v>10.93123660069514</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5433,22 +5433,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.09791149488829938</v>
+        <v>0.09768382681169455</v>
       </c>
       <c r="C51">
-        <v>51.25528472830985</v>
+        <v>50.36313871390088</v>
       </c>
       <c r="D51">
-        <v>61.57878472830986</v>
+        <v>61.63813871390088</v>
       </c>
       <c r="E51">
-        <v>42.1735</v>
+        <v>43.125</v>
       </c>
       <c r="F51">
-        <v>46.6235</v>
+        <v>47.575</v>
       </c>
       <c r="G51">
         <v>36.3</v>
@@ -5469,28 +5469,28 @@
         <v>26.4</v>
       </c>
       <c r="M51">
-        <v>2.4150973</v>
+        <v>2.464385</v>
       </c>
       <c r="N51">
-        <v>23.9849027</v>
+        <v>23.935615</v>
       </c>
       <c r="O51">
-        <v>5.996225675</v>
+        <v>5.98390375</v>
       </c>
       <c r="P51">
-        <v>17.988677025</v>
+        <v>17.95171125</v>
       </c>
       <c r="Q51">
-        <v>20.488677025</v>
+        <v>20.45171125</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1546568527221557</v>
+        <v>0.1565176536233891</v>
       </c>
       <c r="T51">
-        <v>1.583999845148348</v>
+        <v>1.611076765578235</v>
       </c>
       <c r="U51">
         <v>0.0518</v>
@@ -5507,7 +5507,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>10.93123660069514</v>
+        <v>10.71261186868123</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5515,22 +5515,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.09768382681169455</v>
+        <v>0.0974561587350897</v>
       </c>
       <c r="C52">
-        <v>50.36313871390088</v>
+        <v>49.4711072290174</v>
       </c>
       <c r="D52">
-        <v>61.63813871390088</v>
+        <v>61.6976072290174</v>
       </c>
       <c r="E52">
-        <v>43.125</v>
+        <v>44.0765</v>
       </c>
       <c r="F52">
-        <v>47.575</v>
+        <v>48.52650000000001</v>
       </c>
       <c r="G52">
         <v>36.3</v>
@@ -5551,28 +5551,28 @@
         <v>26.4</v>
       </c>
       <c r="M52">
-        <v>2.464385</v>
+        <v>2.5136727</v>
       </c>
       <c r="N52">
-        <v>23.935615</v>
+        <v>23.8863273</v>
       </c>
       <c r="O52">
-        <v>5.98390375</v>
+        <v>5.971581824999999</v>
       </c>
       <c r="P52">
-        <v>17.95171125</v>
+        <v>17.914745475</v>
       </c>
       <c r="Q52">
-        <v>20.45171125</v>
+        <v>20.414745475</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1565176536233891</v>
+        <v>0.1584544055818157</v>
       </c>
       <c r="T52">
-        <v>1.611076765578235</v>
+        <v>1.639258866433831</v>
       </c>
       <c r="U52">
         <v>0.0518</v>
@@ -5589,7 +5589,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>10.71261186868123</v>
+        <v>10.50256065556983</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5597,22 +5597,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.0974561587350897</v>
+        <v>0.09722849065848485</v>
       </c>
       <c r="C53">
-        <v>49.4711072290174</v>
+        <v>48.579190605474</v>
       </c>
       <c r="D53">
-        <v>61.6976072290174</v>
+        <v>61.75719060547401</v>
       </c>
       <c r="E53">
-        <v>44.0765</v>
+        <v>45.028</v>
       </c>
       <c r="F53">
-        <v>48.52650000000001</v>
+        <v>49.478</v>
       </c>
       <c r="G53">
         <v>36.3</v>
@@ -5633,28 +5633,28 @@
         <v>26.4</v>
       </c>
       <c r="M53">
-        <v>2.5136727</v>
+        <v>2.5629604</v>
       </c>
       <c r="N53">
-        <v>23.8863273</v>
+        <v>23.8370396</v>
       </c>
       <c r="O53">
-        <v>5.971581824999999</v>
+        <v>5.959259899999999</v>
       </c>
       <c r="P53">
-        <v>17.914745475</v>
+        <v>17.8777797</v>
       </c>
       <c r="Q53">
-        <v>20.414745475</v>
+        <v>20.3777797</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1584544055818157</v>
+        <v>0.1604718555385101</v>
       </c>
       <c r="T53">
-        <v>1.639258866433831</v>
+        <v>1.668615221491743</v>
       </c>
       <c r="U53">
         <v>0.0518</v>
@@ -5671,7 +5671,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>10.50256065556983</v>
+        <v>10.30058833527042</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5679,22 +5679,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.09722849065848485</v>
+        <v>0.09700082258188002</v>
       </c>
       <c r="C54">
-        <v>48.579190605474</v>
+        <v>47.68738917636834</v>
       </c>
       <c r="D54">
-        <v>61.75719060547401</v>
+        <v>61.81688917636834</v>
       </c>
       <c r="E54">
-        <v>45.028</v>
+        <v>45.9795</v>
       </c>
       <c r="F54">
-        <v>49.478</v>
+        <v>50.4295</v>
       </c>
       <c r="G54">
         <v>36.3</v>
@@ -5715,28 +5715,28 @@
         <v>26.4</v>
       </c>
       <c r="M54">
-        <v>2.5629604</v>
+        <v>2.6122481</v>
       </c>
       <c r="N54">
-        <v>23.8370396</v>
+        <v>23.7877519</v>
       </c>
       <c r="O54">
-        <v>5.959259899999999</v>
+        <v>5.946937975</v>
       </c>
       <c r="P54">
-        <v>17.8777797</v>
+        <v>17.840813925</v>
       </c>
       <c r="Q54">
-        <v>20.3777797</v>
+        <v>20.340813925</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1604718555385101</v>
+        <v>0.162575154429532</v>
       </c>
       <c r="T54">
-        <v>1.668615221491743</v>
+        <v>1.699220783147865</v>
       </c>
       <c r="U54">
         <v>0.0518</v>
@@ -5753,7 +5753,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>10.30058833527042</v>
+        <v>10.10623761196343</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5761,22 +5761,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.09700082258188002</v>
+        <v>0.09677315450527517</v>
       </c>
       <c r="C55">
-        <v>47.68738917636834</v>
+        <v>46.79570327608723</v>
       </c>
       <c r="D55">
-        <v>61.81688917636834</v>
+        <v>61.87670327608725</v>
       </c>
       <c r="E55">
-        <v>45.9795</v>
+        <v>46.931</v>
       </c>
       <c r="F55">
-        <v>50.4295</v>
+        <v>51.38100000000001</v>
       </c>
       <c r="G55">
         <v>36.3</v>
@@ -5797,28 +5797,28 @@
         <v>26.4</v>
       </c>
       <c r="M55">
-        <v>2.6122481</v>
+        <v>2.6615358</v>
       </c>
       <c r="N55">
-        <v>23.7877519</v>
+        <v>23.7384642</v>
       </c>
       <c r="O55">
-        <v>5.946937975</v>
+        <v>5.93461605</v>
       </c>
       <c r="P55">
-        <v>17.840813925</v>
+        <v>17.80384815</v>
       </c>
       <c r="Q55">
-        <v>20.340813925</v>
+        <v>20.30384815</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.162575154429532</v>
+        <v>0.1647699010984243</v>
       </c>
       <c r="T55">
-        <v>1.699220783147865</v>
+        <v>1.73115702139773</v>
       </c>
       <c r="U55">
         <v>0.0518</v>
@@ -5835,7 +5835,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>10.10623761196343</v>
+        <v>9.919085063593734</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5843,22 +5843,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.09677315450527517</v>
+        <v>0.09724673642867034</v>
       </c>
       <c r="C56">
-        <v>46.79570327608723</v>
+        <v>45.71991123418228</v>
       </c>
       <c r="D56">
-        <v>61.87670327608725</v>
+        <v>61.75241123418229</v>
       </c>
       <c r="E56">
-        <v>46.931</v>
+        <v>47.88250000000001</v>
       </c>
       <c r="F56">
-        <v>51.38100000000001</v>
+        <v>52.33250000000001</v>
       </c>
       <c r="G56">
         <v>36.3</v>
@@ -5879,45 +5879,45 @@
         <v>26.4</v>
       </c>
       <c r="M56">
-        <v>2.6615358</v>
+        <v>2.79978875</v>
       </c>
       <c r="N56">
-        <v>23.7384642</v>
+        <v>23.60021125</v>
       </c>
       <c r="O56">
-        <v>5.93461605</v>
+        <v>5.900052812499999</v>
       </c>
       <c r="P56">
-        <v>17.80384815</v>
+        <v>17.7001584375</v>
       </c>
       <c r="Q56">
-        <v>20.30384815</v>
+        <v>20.2001584375</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1647699010984243</v>
+        <v>0.1670621920637119</v>
       </c>
       <c r="T56">
-        <v>1.73115702139773</v>
+        <v>1.764512648014257</v>
       </c>
       <c r="U56">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V56">
         <v>0.25</v>
       </c>
       <c r="W56">
-        <v>0.03885</v>
+        <v>0.040125</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y56">
-        <v>9.919085063593734</v>
+        <v>9.429282834285264</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5925,22 +5925,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.09724673642867034</v>
+        <v>0.09703181835206549</v>
       </c>
       <c r="C57">
-        <v>45.71991123418228</v>
+        <v>44.82475475451578</v>
       </c>
       <c r="D57">
-        <v>61.75241123418229</v>
+        <v>61.80875475451579</v>
       </c>
       <c r="E57">
-        <v>47.88250000000001</v>
+        <v>48.834</v>
       </c>
       <c r="F57">
-        <v>52.33250000000001</v>
+        <v>53.28400000000001</v>
       </c>
       <c r="G57">
         <v>36.3</v>
@@ -5961,28 +5961,28 @@
         <v>26.4</v>
       </c>
       <c r="M57">
-        <v>2.79978875</v>
+        <v>2.850694</v>
       </c>
       <c r="N57">
-        <v>23.60021125</v>
+        <v>23.549306</v>
       </c>
       <c r="O57">
-        <v>5.900052812499999</v>
+        <v>5.887326499999999</v>
       </c>
       <c r="P57">
-        <v>17.7001584375</v>
+        <v>17.6619795</v>
       </c>
       <c r="Q57">
-        <v>20.2001584375</v>
+        <v>20.1619795</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1670621920637119</v>
+        <v>0.1694586780728761</v>
       </c>
       <c r="T57">
-        <v>1.764512648014257</v>
+        <v>1.799384439476989</v>
       </c>
       <c r="U57">
         <v>0.0535</v>
@@ -5999,7 +5999,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>9.429282834285264</v>
+        <v>9.260902783673027</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6007,22 +6007,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.09703181835206549</v>
+        <v>0.09681690027546067</v>
       </c>
       <c r="C58">
-        <v>44.82475475451578</v>
+        <v>43.92970118553391</v>
       </c>
       <c r="D58">
-        <v>61.80875475451579</v>
+        <v>61.86520118553392</v>
       </c>
       <c r="E58">
-        <v>48.834</v>
+        <v>49.78550000000001</v>
       </c>
       <c r="F58">
-        <v>53.28400000000001</v>
+        <v>54.23550000000001</v>
       </c>
       <c r="G58">
         <v>36.3</v>
@@ -6043,28 +6043,28 @@
         <v>26.4</v>
       </c>
       <c r="M58">
-        <v>2.850694</v>
+        <v>2.90159925</v>
       </c>
       <c r="N58">
-        <v>23.549306</v>
+        <v>23.49840075</v>
       </c>
       <c r="O58">
-        <v>5.887326499999999</v>
+        <v>5.8746001875</v>
       </c>
       <c r="P58">
-        <v>17.6619795</v>
+        <v>17.6238005625</v>
       </c>
       <c r="Q58">
-        <v>20.1619795</v>
+        <v>20.1238005625</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1694586780728761</v>
+        <v>0.1719666285475829</v>
       </c>
       <c r="T58">
-        <v>1.799384439476989</v>
+        <v>1.835878174728686</v>
       </c>
       <c r="U58">
         <v>0.0535</v>
@@ -6081,7 +6081,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>9.260902783673027</v>
+        <v>9.098430805012097</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6089,22 +6089,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.09681690027546067</v>
+        <v>0.09660198219885581</v>
       </c>
       <c r="C59">
-        <v>43.92970118553391</v>
+        <v>43.03475080944186</v>
       </c>
       <c r="D59">
-        <v>61.86520118553392</v>
+        <v>61.92175080944187</v>
       </c>
       <c r="E59">
-        <v>49.78550000000001</v>
+        <v>50.73700000000001</v>
       </c>
       <c r="F59">
-        <v>54.23550000000001</v>
+        <v>55.18700000000001</v>
       </c>
       <c r="G59">
         <v>36.3</v>
@@ -6125,28 +6125,28 @@
         <v>26.4</v>
       </c>
       <c r="M59">
-        <v>2.90159925</v>
+        <v>2.952504500000001</v>
       </c>
       <c r="N59">
-        <v>23.49840075</v>
+        <v>23.4474955</v>
       </c>
       <c r="O59">
-        <v>5.8746001875</v>
+        <v>5.861873875</v>
       </c>
       <c r="P59">
-        <v>17.6238005625</v>
+        <v>17.585621625</v>
       </c>
       <c r="Q59">
-        <v>20.1238005625</v>
+        <v>20.085621625</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1719666285475829</v>
+        <v>0.174594005235371</v>
       </c>
       <c r="T59">
-        <v>1.835878174728686</v>
+        <v>1.87410970689713</v>
       </c>
       <c r="U59">
         <v>0.0535</v>
@@ -6163,7 +6163,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>9.098430805012097</v>
+        <v>8.941561308373956</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6171,22 +6171,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.09660198219885581</v>
+        <v>0.09638706412225098</v>
       </c>
       <c r="C60">
-        <v>43.03475080944187</v>
+        <v>42.13990390947762</v>
       </c>
       <c r="D60">
-        <v>61.92175080944187</v>
+        <v>61.97840390947762</v>
       </c>
       <c r="E60">
-        <v>50.73699999999999</v>
+        <v>51.6885</v>
       </c>
       <c r="F60">
-        <v>55.187</v>
+        <v>56.1385</v>
       </c>
       <c r="G60">
         <v>36.3</v>
@@ -6207,28 +6207,28 @@
         <v>26.4</v>
       </c>
       <c r="M60">
-        <v>2.9525045</v>
+        <v>3.00340975</v>
       </c>
       <c r="N60">
-        <v>23.4474955</v>
+        <v>23.39659025</v>
       </c>
       <c r="O60">
-        <v>5.861873875</v>
+        <v>5.8491475625</v>
       </c>
       <c r="P60">
-        <v>17.585621625</v>
+        <v>17.5474426875</v>
       </c>
       <c r="Q60">
-        <v>20.085621625</v>
+        <v>20.0474426875</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.174594005235371</v>
+        <v>0.1773495466396365</v>
       </c>
       <c r="T60">
-        <v>1.87410970689713</v>
+        <v>1.914206191854279</v>
       </c>
       <c r="U60">
         <v>0.0535</v>
@@ -6245,7 +6245,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>8.941561308373959</v>
+        <v>8.79000942179135</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6253,22 +6253,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.09638706412225098</v>
+        <v>0.09617214604564614</v>
       </c>
       <c r="C61">
-        <v>42.13990390947762</v>
+        <v>41.24516076991665</v>
       </c>
       <c r="D61">
-        <v>61.97840390947762</v>
+        <v>62.03516076991666</v>
       </c>
       <c r="E61">
-        <v>51.6885</v>
+        <v>52.64</v>
       </c>
       <c r="F61">
-        <v>56.1385</v>
+        <v>57.09</v>
       </c>
       <c r="G61">
         <v>36.3</v>
@@ -6289,28 +6289,28 @@
         <v>26.4</v>
       </c>
       <c r="M61">
-        <v>3.00340975</v>
+        <v>3.054315</v>
       </c>
       <c r="N61">
-        <v>23.39659025</v>
+        <v>23.345685</v>
       </c>
       <c r="O61">
-        <v>5.8491475625</v>
+        <v>5.83642125</v>
       </c>
       <c r="P61">
-        <v>17.5474426875</v>
+        <v>17.50926375</v>
       </c>
       <c r="Q61">
-        <v>20.0474426875</v>
+        <v>20.00926375</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1773495466396365</v>
+        <v>0.1802428651141153</v>
       </c>
       <c r="T61">
-        <v>1.914206191854279</v>
+        <v>1.956307501059285</v>
       </c>
       <c r="U61">
         <v>0.0535</v>
@@ -6327,7 +6327,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>8.79000942179135</v>
+        <v>8.643509264761493</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6335,22 +6335,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.09617214604564614</v>
+        <v>0.09595722796904131</v>
       </c>
       <c r="C62">
-        <v>41.24516076991665</v>
+        <v>40.35052167607671</v>
       </c>
       <c r="D62">
-        <v>62.03516076991666</v>
+        <v>62.09202167607671</v>
       </c>
       <c r="E62">
-        <v>52.64</v>
+        <v>53.5915</v>
       </c>
       <c r="F62">
-        <v>57.09</v>
+        <v>58.0415</v>
       </c>
       <c r="G62">
         <v>36.3</v>
@@ -6371,28 +6371,28 @@
         <v>26.4</v>
       </c>
       <c r="M62">
-        <v>3.054315</v>
+        <v>3.10522025</v>
       </c>
       <c r="N62">
-        <v>23.345685</v>
+        <v>23.29477975</v>
       </c>
       <c r="O62">
-        <v>5.83642125</v>
+        <v>5.8236949375</v>
       </c>
       <c r="P62">
-        <v>17.50926375</v>
+        <v>17.4710848125</v>
       </c>
       <c r="Q62">
-        <v>20.00926375</v>
+        <v>19.9710848125</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1802428651141153</v>
+        <v>0.1832845588949777</v>
       </c>
       <c r="T62">
-        <v>1.956307501059285</v>
+        <v>2.000567851761984</v>
       </c>
       <c r="U62">
         <v>0.0535</v>
@@ -6409,7 +6409,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>8.643509264761493</v>
+        <v>8.501812391568681</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6417,22 +6417,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.09595722796904131</v>
+        <v>0.09574230989243644</v>
       </c>
       <c r="C63">
-        <v>40.35052167607671</v>
+        <v>39.45598691432257</v>
       </c>
       <c r="D63">
-        <v>62.09202167607671</v>
+        <v>62.14898691432258</v>
       </c>
       <c r="E63">
-        <v>53.5915</v>
+        <v>54.543</v>
       </c>
       <c r="F63">
-        <v>58.0415</v>
+        <v>58.993</v>
       </c>
       <c r="G63">
         <v>36.3</v>
@@ -6453,28 +6453,28 @@
         <v>26.4</v>
       </c>
       <c r="M63">
-        <v>3.10522025</v>
+        <v>3.1561255</v>
       </c>
       <c r="N63">
-        <v>23.29477975</v>
+        <v>23.2438745</v>
       </c>
       <c r="O63">
-        <v>5.8236949375</v>
+        <v>5.810968624999999</v>
       </c>
       <c r="P63">
-        <v>17.4710848125</v>
+        <v>17.432905875</v>
       </c>
       <c r="Q63">
-        <v>19.9710848125</v>
+        <v>19.932905875</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1832845588949777</v>
+        <v>0.1864863418222012</v>
       </c>
       <c r="T63">
-        <v>2.000567851761984</v>
+        <v>2.04715769460693</v>
       </c>
       <c r="U63">
         <v>0.0535</v>
@@ -6491,7 +6491,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>8.501812391568681</v>
+        <v>8.364686385253057</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6499,22 +6499,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.09574230989243644</v>
+        <v>0.09552739181583161</v>
       </c>
       <c r="C64">
-        <v>39.45598691432257</v>
+        <v>38.56155677207083</v>
       </c>
       <c r="D64">
-        <v>62.14898691432258</v>
+        <v>62.20605677207084</v>
       </c>
       <c r="E64">
-        <v>54.543</v>
+        <v>55.4945</v>
       </c>
       <c r="F64">
-        <v>58.993</v>
+        <v>59.94450000000001</v>
       </c>
       <c r="G64">
         <v>36.3</v>
@@ -6535,28 +6535,28 @@
         <v>26.4</v>
       </c>
       <c r="M64">
-        <v>3.1561255</v>
+        <v>3.20703075</v>
       </c>
       <c r="N64">
-        <v>23.2438745</v>
+        <v>23.19296925</v>
       </c>
       <c r="O64">
-        <v>5.810968624999999</v>
+        <v>5.798242312499999</v>
       </c>
       <c r="P64">
-        <v>17.432905875</v>
+        <v>17.3947269375</v>
       </c>
       <c r="Q64">
-        <v>19.932905875</v>
+        <v>19.8947269375</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1864863418222012</v>
+        <v>0.1898611940968422</v>
       </c>
       <c r="T64">
-        <v>2.04715769460693</v>
+        <v>2.096265907335386</v>
       </c>
       <c r="U64">
         <v>0.0535</v>
@@ -6573,7 +6573,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>8.364686385253057</v>
+        <v>8.231913585487135</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6581,22 +6581,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.09552739181583161</v>
+        <v>0.09531247373922677</v>
       </c>
       <c r="C65">
-        <v>38.56155677207083</v>
+        <v>37.66723153779481</v>
       </c>
       <c r="D65">
-        <v>62.20605677207084</v>
+        <v>62.26323153779482</v>
       </c>
       <c r="E65">
-        <v>55.4945</v>
+        <v>56.44600000000001</v>
       </c>
       <c r="F65">
-        <v>59.94450000000001</v>
+        <v>60.89600000000001</v>
       </c>
       <c r="G65">
         <v>36.3</v>
@@ -6617,28 +6617,28 @@
         <v>26.4</v>
       </c>
       <c r="M65">
-        <v>3.20703075</v>
+        <v>3.257936</v>
       </c>
       <c r="N65">
-        <v>23.19296925</v>
+        <v>23.142064</v>
       </c>
       <c r="O65">
-        <v>5.798242312499999</v>
+        <v>5.785515999999999</v>
       </c>
       <c r="P65">
-        <v>17.3947269375</v>
+        <v>17.356548</v>
       </c>
       <c r="Q65">
-        <v>19.8947269375</v>
+        <v>19.856548</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1898611940968422</v>
+        <v>0.1934235381645188</v>
       </c>
       <c r="T65">
-        <v>2.096265907335386</v>
+        <v>2.148102354104313</v>
       </c>
       <c r="U65">
         <v>0.0535</v>
@@ -6655,7 +6655,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>8.231913585487135</v>
+        <v>8.103289935713899</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6663,22 +6663,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.09531247373922677</v>
+        <v>0.09509755566262192</v>
       </c>
       <c r="C66">
-        <v>37.66723153779481</v>
+        <v>36.77301150102935</v>
       </c>
       <c r="D66">
-        <v>62.26323153779482</v>
+        <v>62.32051150102936</v>
       </c>
       <c r="E66">
-        <v>56.44600000000001</v>
+        <v>57.3975</v>
       </c>
       <c r="F66">
-        <v>60.89600000000001</v>
+        <v>61.8475</v>
       </c>
       <c r="G66">
         <v>36.3</v>
@@ -6699,28 +6699,28 @@
         <v>26.4</v>
       </c>
       <c r="M66">
-        <v>3.257936</v>
+        <v>3.30884125</v>
       </c>
       <c r="N66">
-        <v>23.142064</v>
+        <v>23.09115875</v>
       </c>
       <c r="O66">
-        <v>5.785515999999999</v>
+        <v>5.7727896875</v>
       </c>
       <c r="P66">
-        <v>17.356548</v>
+        <v>17.3183690625</v>
       </c>
       <c r="Q66">
-        <v>19.856548</v>
+        <v>19.8183690625</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1934235381645188</v>
+        <v>0.1971894447503484</v>
       </c>
       <c r="T66">
-        <v>2.148102354104313</v>
+        <v>2.20290088354575</v>
       </c>
       <c r="U66">
         <v>0.0535</v>
@@ -6737,7 +6737,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>8.103289935713899</v>
+        <v>7.978623936702916</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6745,22 +6745,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.09509755566262192</v>
+        <v>0.09488263758601709</v>
       </c>
       <c r="C67">
-        <v>36.77301150102935</v>
+        <v>35.87889695237573</v>
       </c>
       <c r="D67">
-        <v>62.32051150102936</v>
+        <v>62.37789695237573</v>
       </c>
       <c r="E67">
-        <v>57.3975</v>
+        <v>58.349</v>
       </c>
       <c r="F67">
-        <v>61.8475</v>
+        <v>62.79900000000001</v>
       </c>
       <c r="G67">
         <v>36.3</v>
@@ -6781,28 +6781,28 @@
         <v>26.4</v>
       </c>
       <c r="M67">
-        <v>3.30884125</v>
+        <v>3.3597465</v>
       </c>
       <c r="N67">
-        <v>23.09115875</v>
+        <v>23.0402535</v>
       </c>
       <c r="O67">
-        <v>5.7727896875</v>
+        <v>5.760063375</v>
       </c>
       <c r="P67">
-        <v>17.3183690625</v>
+        <v>17.280190125</v>
       </c>
       <c r="Q67">
-        <v>19.8183690625</v>
+        <v>19.780190125</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1971894447503484</v>
+        <v>0.2011768752529914</v>
       </c>
       <c r="T67">
-        <v>2.20290088354575</v>
+        <v>2.260922855895506</v>
       </c>
       <c r="U67">
         <v>0.0535</v>
@@ -6819,7 +6819,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>7.978623936702916</v>
+        <v>7.85773569523772</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6827,22 +6827,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.09488263758601709</v>
+        <v>0.09466771950941223</v>
       </c>
       <c r="C68">
-        <v>35.87889695237573</v>
+        <v>34.98488818350655</v>
       </c>
       <c r="D68">
-        <v>62.37789695237573</v>
+        <v>62.43538818350655</v>
       </c>
       <c r="E68">
-        <v>58.349</v>
+        <v>59.30050000000001</v>
       </c>
       <c r="F68">
-        <v>62.79900000000001</v>
+        <v>63.75050000000001</v>
       </c>
       <c r="G68">
         <v>36.3</v>
@@ -6863,28 +6863,28 @@
         <v>26.4</v>
       </c>
       <c r="M68">
-        <v>3.3597465</v>
+        <v>3.41065175</v>
       </c>
       <c r="N68">
-        <v>23.0402535</v>
+        <v>22.98934825</v>
       </c>
       <c r="O68">
-        <v>5.760063375</v>
+        <v>5.7473370625</v>
       </c>
       <c r="P68">
-        <v>17.280190125</v>
+        <v>17.2420111875</v>
       </c>
       <c r="Q68">
-        <v>19.780190125</v>
+        <v>19.7420111875</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.2011768752529914</v>
+        <v>0.2054059682103401</v>
       </c>
       <c r="T68">
-        <v>2.260922855895506</v>
+        <v>2.322461311417975</v>
       </c>
       <c r="U68">
         <v>0.0535</v>
@@ -6901,7 +6901,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>7.85773569523772</v>
+        <v>7.740456057995366</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6909,22 +6909,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.09466771950941223</v>
+        <v>0.09445280143280739</v>
       </c>
       <c r="C69">
-        <v>34.98488818350655</v>
+        <v>34.0909854871707</v>
       </c>
       <c r="D69">
-        <v>62.43538818350655</v>
+        <v>62.49298548717071</v>
       </c>
       <c r="E69">
-        <v>59.30050000000001</v>
+        <v>60.25200000000001</v>
       </c>
       <c r="F69">
-        <v>63.75050000000001</v>
+        <v>64.70200000000001</v>
       </c>
       <c r="G69">
         <v>36.3</v>
@@ -6945,28 +6945,28 @@
         <v>26.4</v>
       </c>
       <c r="M69">
-        <v>3.41065175</v>
+        <v>3.461557</v>
       </c>
       <c r="N69">
-        <v>22.98934825</v>
+        <v>22.938443</v>
       </c>
       <c r="O69">
-        <v>5.7473370625</v>
+        <v>5.73461075</v>
       </c>
       <c r="P69">
-        <v>17.2420111875</v>
+        <v>17.20383225</v>
       </c>
       <c r="Q69">
-        <v>19.7420111875</v>
+        <v>19.70383225</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.2054059682103401</v>
+        <v>0.2098993794775231</v>
       </c>
       <c r="T69">
-        <v>2.322461311417975</v>
+        <v>2.387845920410598</v>
       </c>
       <c r="U69">
         <v>0.0535</v>
@@ -6983,7 +6983,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>7.740456057995366</v>
+        <v>7.626625821848375</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6991,22 +6991,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.09445280143280739</v>
+        <v>0.09465188335620256</v>
       </c>
       <c r="C70">
-        <v>34.0909854871707</v>
+        <v>33.08612859439376</v>
       </c>
       <c r="D70">
-        <v>62.49298548717071</v>
+        <v>62.43962859439377</v>
       </c>
       <c r="E70">
-        <v>60.25200000000001</v>
+        <v>61.20350000000001</v>
       </c>
       <c r="F70">
-        <v>64.70200000000001</v>
+        <v>65.65350000000001</v>
       </c>
       <c r="G70">
         <v>36.3</v>
@@ -7027,45 +7027,45 @@
         <v>26.4</v>
       </c>
       <c r="M70">
-        <v>3.461557</v>
+        <v>3.564985050000001</v>
       </c>
       <c r="N70">
-        <v>22.938443</v>
+        <v>22.83501495</v>
       </c>
       <c r="O70">
-        <v>5.73461075</v>
+        <v>5.708753737499999</v>
       </c>
       <c r="P70">
-        <v>17.20383225</v>
+        <v>17.1262612125</v>
       </c>
       <c r="Q70">
-        <v>19.70383225</v>
+        <v>19.6262612125</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.2098993794775231</v>
+        <v>0.2146826882458147</v>
       </c>
       <c r="T70">
-        <v>2.387845920410598</v>
+        <v>2.457448891273713</v>
       </c>
       <c r="U70">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V70">
         <v>0.25</v>
       </c>
       <c r="W70">
-        <v>0.040125</v>
+        <v>0.040725</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y70">
-        <v>7.626625821848375</v>
+        <v>7.405360648006082</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7073,22 +7073,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.09465188335620256</v>
+        <v>0.09444296527959771</v>
       </c>
       <c r="C71">
-        <v>33.08612859439376</v>
+        <v>32.19062408551538</v>
       </c>
       <c r="D71">
-        <v>62.43962859439377</v>
+        <v>62.49562408551538</v>
       </c>
       <c r="E71">
-        <v>61.20350000000001</v>
+        <v>62.155</v>
       </c>
       <c r="F71">
-        <v>65.65350000000001</v>
+        <v>66.605</v>
       </c>
       <c r="G71">
         <v>36.3</v>
@@ -7109,28 +7109,28 @@
         <v>26.4</v>
       </c>
       <c r="M71">
-        <v>3.564985050000001</v>
+        <v>3.6166515</v>
       </c>
       <c r="N71">
-        <v>22.83501495</v>
+        <v>22.7833485</v>
       </c>
       <c r="O71">
-        <v>5.708753737499999</v>
+        <v>5.695837125</v>
       </c>
       <c r="P71">
-        <v>17.1262612125</v>
+        <v>17.087511375</v>
       </c>
       <c r="Q71">
-        <v>19.6262612125</v>
+        <v>19.587511375</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.2146826882458147</v>
+        <v>0.2197848842653257</v>
       </c>
       <c r="T71">
-        <v>2.457448891273713</v>
+        <v>2.531692060194369</v>
       </c>
       <c r="U71">
         <v>0.0543</v>
@@ -7147,7 +7147,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>7.405360648006082</v>
+        <v>7.299569781605996</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7155,22 +7155,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.09444296527959771</v>
+        <v>0.09423404720299287</v>
       </c>
       <c r="C72">
-        <v>32.19062408551538</v>
+        <v>31.2952200996386</v>
       </c>
       <c r="D72">
-        <v>62.49562408551538</v>
+        <v>62.55172009963862</v>
       </c>
       <c r="E72">
-        <v>62.155</v>
+        <v>63.10650000000001</v>
       </c>
       <c r="F72">
-        <v>66.605</v>
+        <v>67.55650000000001</v>
       </c>
       <c r="G72">
         <v>36.3</v>
@@ -7191,28 +7191,28 @@
         <v>26.4</v>
       </c>
       <c r="M72">
-        <v>3.6166515</v>
+        <v>3.668317950000001</v>
       </c>
       <c r="N72">
-        <v>22.7833485</v>
+        <v>22.73168205</v>
       </c>
       <c r="O72">
-        <v>5.695837125</v>
+        <v>5.682920512499999</v>
       </c>
       <c r="P72">
-        <v>17.087511375</v>
+        <v>17.0487615375</v>
       </c>
       <c r="Q72">
-        <v>19.587511375</v>
+        <v>19.5487615375</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.2197848842653257</v>
+        <v>0.2252389558723893</v>
       </c>
       <c r="T72">
-        <v>2.531692060194369</v>
+        <v>2.611055447661277</v>
       </c>
       <c r="U72">
         <v>0.0543</v>
@@ -7229,7 +7229,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>7.299569781605996</v>
+        <v>7.196758939611543</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7237,22 +7237,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.09423404720299289</v>
+        <v>0.09402512912638802</v>
       </c>
       <c r="C73">
-        <v>31.29522009963861</v>
+        <v>30.39991690769473</v>
       </c>
       <c r="D73">
-        <v>62.55172009963862</v>
+        <v>62.60791690769473</v>
       </c>
       <c r="E73">
-        <v>63.1065</v>
+        <v>64.05799999999999</v>
       </c>
       <c r="F73">
-        <v>67.5565</v>
+        <v>68.508</v>
       </c>
       <c r="G73">
         <v>36.3</v>
@@ -7273,28 +7273,28 @@
         <v>26.4</v>
       </c>
       <c r="M73">
-        <v>3.66831795</v>
+        <v>3.7199844</v>
       </c>
       <c r="N73">
-        <v>22.73168205</v>
+        <v>22.6800156</v>
       </c>
       <c r="O73">
-        <v>5.6829205125</v>
+        <v>5.670003899999999</v>
       </c>
       <c r="P73">
-        <v>17.0487615375</v>
+        <v>17.0100117</v>
       </c>
       <c r="Q73">
-        <v>19.5487615375</v>
+        <v>19.5100117</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.2252389558723892</v>
+        <v>0.2310826040228144</v>
       </c>
       <c r="T73">
-        <v>2.611055447661277</v>
+        <v>2.696087648518678</v>
       </c>
       <c r="U73">
         <v>0.0543</v>
@@ -7311,7 +7311,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>7.196758939611546</v>
+        <v>7.096803954339163</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7319,22 +7319,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.09402512912638802</v>
+        <v>0.09381621104978319</v>
       </c>
       <c r="C74">
-        <v>30.39991690769473</v>
+        <v>29.50471478158944</v>
       </c>
       <c r="D74">
-        <v>62.60791690769473</v>
+        <v>62.66421478158946</v>
       </c>
       <c r="E74">
-        <v>64.05799999999999</v>
+        <v>65.0095</v>
       </c>
       <c r="F74">
-        <v>68.508</v>
+        <v>69.45950000000001</v>
       </c>
       <c r="G74">
         <v>36.3</v>
@@ -7355,28 +7355,28 @@
         <v>26.4</v>
       </c>
       <c r="M74">
-        <v>3.7199844</v>
+        <v>3.77165085</v>
       </c>
       <c r="N74">
-        <v>22.6800156</v>
+        <v>22.62834915</v>
       </c>
       <c r="O74">
-        <v>5.670003899999999</v>
+        <v>5.6570872875</v>
       </c>
       <c r="P74">
-        <v>17.0100117</v>
+        <v>16.9712618625</v>
       </c>
       <c r="Q74">
-        <v>19.5100117</v>
+        <v>19.4712618625</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.2310826040228144</v>
+        <v>0.237359114999197</v>
       </c>
       <c r="T74">
-        <v>2.696087648518678</v>
+        <v>2.787418530921072</v>
       </c>
       <c r="U74">
         <v>0.0543</v>
@@ -7393,7 +7393,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>7.096803954339163</v>
+        <v>6.999587461813968</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7401,22 +7401,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.09381621104978319</v>
+        <v>0.09360729297317834</v>
       </c>
       <c r="C75">
-        <v>29.50471478158944</v>
+        <v>28.60961399420744</v>
       </c>
       <c r="D75">
-        <v>62.66421478158946</v>
+        <v>62.72061399420744</v>
       </c>
       <c r="E75">
-        <v>65.0095</v>
+        <v>65.961</v>
       </c>
       <c r="F75">
-        <v>69.45950000000001</v>
+        <v>70.411</v>
       </c>
       <c r="G75">
         <v>36.3</v>
@@ -7437,28 +7437,28 @@
         <v>26.4</v>
       </c>
       <c r="M75">
-        <v>3.77165085</v>
+        <v>3.8233173</v>
       </c>
       <c r="N75">
-        <v>22.62834915</v>
+        <v>22.5766827</v>
       </c>
       <c r="O75">
-        <v>5.6570872875</v>
+        <v>5.644170675</v>
       </c>
       <c r="P75">
-        <v>16.9712618625</v>
+        <v>16.932512025</v>
       </c>
       <c r="Q75">
-        <v>19.4712618625</v>
+        <v>19.432512025</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.237359114999197</v>
+        <v>0.2441184345122244</v>
       </c>
       <c r="T75">
-        <v>2.787418530921072</v>
+        <v>2.885774865815958</v>
       </c>
       <c r="U75">
         <v>0.0543</v>
@@ -7475,7 +7475,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>6.999587461813968</v>
+        <v>6.904998442059726</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7483,22 +7483,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.09360729297317834</v>
+        <v>0.0933983748965735</v>
       </c>
       <c r="C76">
-        <v>28.60961399420744</v>
+        <v>27.71461481941657</v>
       </c>
       <c r="D76">
-        <v>62.72061399420744</v>
+        <v>62.77711481941659</v>
       </c>
       <c r="E76">
-        <v>65.961</v>
+        <v>66.91250000000001</v>
       </c>
       <c r="F76">
-        <v>70.411</v>
+        <v>71.36250000000001</v>
       </c>
       <c r="G76">
         <v>36.3</v>
@@ -7519,28 +7519,28 @@
         <v>26.4</v>
       </c>
       <c r="M76">
-        <v>3.8233173</v>
+        <v>3.874983750000001</v>
       </c>
       <c r="N76">
-        <v>22.5766827</v>
+        <v>22.52501625</v>
       </c>
       <c r="O76">
-        <v>5.644170675</v>
+        <v>5.631254062499999</v>
       </c>
       <c r="P76">
-        <v>16.932512025</v>
+        <v>16.8937621875</v>
       </c>
       <c r="Q76">
-        <v>19.432512025</v>
+        <v>19.3937621875</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.2441184345122244</v>
+        <v>0.251418499586294</v>
       </c>
       <c r="T76">
-        <v>2.885774865815958</v>
+        <v>2.991999707502436</v>
       </c>
       <c r="U76">
         <v>0.0543</v>
@@ -7557,7 +7557,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>6.904998442059726</v>
+        <v>6.812931796165595</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7565,22 +7565,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.0933983748965735</v>
+        <v>0.09318945681996865</v>
       </c>
       <c r="C77">
-        <v>27.71461481941657</v>
+        <v>26.81971753207257</v>
       </c>
       <c r="D77">
-        <v>62.77711481941659</v>
+        <v>62.83371753207258</v>
       </c>
       <c r="E77">
-        <v>66.91250000000001</v>
+        <v>67.864</v>
       </c>
       <c r="F77">
-        <v>71.36250000000001</v>
+        <v>72.31400000000001</v>
       </c>
       <c r="G77">
         <v>36.3</v>
@@ -7601,28 +7601,28 @@
         <v>26.4</v>
       </c>
       <c r="M77">
-        <v>3.874983750000001</v>
+        <v>3.926650200000001</v>
       </c>
       <c r="N77">
-        <v>22.52501625</v>
+        <v>22.4733498</v>
       </c>
       <c r="O77">
-        <v>5.631254062499999</v>
+        <v>5.618337449999999</v>
       </c>
       <c r="P77">
-        <v>16.8937621875</v>
+        <v>16.85501235</v>
       </c>
       <c r="Q77">
-        <v>19.3937621875</v>
+        <v>19.35501235</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.251418499586294</v>
+        <v>0.2593269034165361</v>
       </c>
       <c r="T77">
-        <v>2.991999707502436</v>
+        <v>3.107076619329452</v>
       </c>
       <c r="U77">
         <v>0.0543</v>
@@ -7639,7 +7639,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>6.812931796165595</v>
+        <v>6.723287956742364</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7647,22 +7647,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.09318945681996865</v>
+        <v>0.09298053874336382</v>
       </c>
       <c r="C78">
-        <v>26.81971753207257</v>
+        <v>25.92492240802322</v>
       </c>
       <c r="D78">
-        <v>62.83371753207258</v>
+        <v>62.89042240802323</v>
       </c>
       <c r="E78">
-        <v>67.864</v>
+        <v>68.8155</v>
       </c>
       <c r="F78">
-        <v>72.31400000000001</v>
+        <v>73.2655</v>
       </c>
       <c r="G78">
         <v>36.3</v>
@@ -7683,28 +7683,28 @@
         <v>26.4</v>
       </c>
       <c r="M78">
-        <v>3.926650200000001</v>
+        <v>3.97831665</v>
       </c>
       <c r="N78">
-        <v>22.4733498</v>
+        <v>22.42168335</v>
       </c>
       <c r="O78">
-        <v>5.618337449999999</v>
+        <v>5.6054208375</v>
       </c>
       <c r="P78">
-        <v>16.85501235</v>
+        <v>16.8162625125</v>
       </c>
       <c r="Q78">
-        <v>19.35501235</v>
+        <v>19.3162625125</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.2593269034165361</v>
+        <v>0.2679229945363644</v>
       </c>
       <c r="T78">
-        <v>3.107076619329452</v>
+        <v>3.232160219141427</v>
       </c>
       <c r="U78">
         <v>0.0543</v>
@@ -7721,7 +7721,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>6.723287956742364</v>
+        <v>6.635972528732723</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7729,22 +7729,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.09298053874336382</v>
+        <v>0.09277162066675898</v>
       </c>
       <c r="C79">
-        <v>25.92492240802322</v>
+        <v>25.03022972411304</v>
       </c>
       <c r="D79">
-        <v>62.89042240802323</v>
+        <v>62.94722972411305</v>
       </c>
       <c r="E79">
-        <v>68.8155</v>
+        <v>69.76700000000001</v>
       </c>
       <c r="F79">
-        <v>73.2655</v>
+        <v>74.21700000000001</v>
       </c>
       <c r="G79">
         <v>36.3</v>
@@ -7765,28 +7765,28 @@
         <v>26.4</v>
       </c>
       <c r="M79">
-        <v>3.97831665</v>
+        <v>4.029983100000001</v>
       </c>
       <c r="N79">
-        <v>22.42168335</v>
+        <v>22.3700169</v>
       </c>
       <c r="O79">
-        <v>5.6054208375</v>
+        <v>5.592504224999999</v>
       </c>
       <c r="P79">
-        <v>16.8162625125</v>
+        <v>16.777512675</v>
       </c>
       <c r="Q79">
-        <v>19.3162625125</v>
+        <v>19.277512675</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.2679229945363644</v>
+        <v>0.2773005484852681</v>
       </c>
       <c r="T79">
-        <v>3.232160219141427</v>
+        <v>3.368615055299945</v>
       </c>
       <c r="U79">
         <v>0.0543</v>
@@ -7803,7 +7803,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>6.635972528732723</v>
+        <v>6.550895957851533</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7811,22 +7811,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.09277162066675898</v>
+        <v>0.09256270259015414</v>
       </c>
       <c r="C80">
-        <v>25.03022972411304</v>
+        <v>24.13563975818771</v>
       </c>
       <c r="D80">
-        <v>62.94722972411305</v>
+        <v>63.00413975818772</v>
       </c>
       <c r="E80">
-        <v>69.76700000000001</v>
+        <v>70.71850000000001</v>
       </c>
       <c r="F80">
-        <v>74.21700000000001</v>
+        <v>75.16850000000001</v>
       </c>
       <c r="G80">
         <v>36.3</v>
@@ -7847,28 +7847,28 @@
         <v>26.4</v>
       </c>
       <c r="M80">
-        <v>4.029983100000001</v>
+        <v>4.081649550000001</v>
       </c>
       <c r="N80">
-        <v>22.3700169</v>
+        <v>22.31835045</v>
       </c>
       <c r="O80">
-        <v>5.592504224999999</v>
+        <v>5.579587612499999</v>
       </c>
       <c r="P80">
-        <v>16.777512675</v>
+        <v>16.7387628375</v>
       </c>
       <c r="Q80">
-        <v>19.277512675</v>
+        <v>19.2387628375</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.2773005484852681</v>
+        <v>0.2875712028102578</v>
       </c>
       <c r="T80">
-        <v>3.368615055299945</v>
+        <v>3.518065590140227</v>
       </c>
       <c r="U80">
         <v>0.0543</v>
@@ -7885,7 +7885,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>6.550895957851533</v>
+        <v>6.467973224207843</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7893,22 +7893,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.09256270259015414</v>
+        <v>0.09235378451354929</v>
       </c>
       <c r="C81">
-        <v>24.13563975818771</v>
+        <v>23.24115278909859</v>
       </c>
       <c r="D81">
-        <v>63.00413975818772</v>
+        <v>63.0611527890986</v>
       </c>
       <c r="E81">
-        <v>70.71850000000001</v>
+        <v>71.67</v>
       </c>
       <c r="F81">
-        <v>75.16850000000001</v>
+        <v>76.12</v>
       </c>
       <c r="G81">
         <v>36.3</v>
@@ -7929,28 +7929,28 @@
         <v>26.4</v>
       </c>
       <c r="M81">
-        <v>4.081649550000001</v>
+        <v>4.133316000000001</v>
       </c>
       <c r="N81">
-        <v>22.31835045</v>
+        <v>22.266684</v>
       </c>
       <c r="O81">
-        <v>5.579587612499999</v>
+        <v>5.566670999999999</v>
       </c>
       <c r="P81">
-        <v>16.7387628375</v>
+        <v>16.700013</v>
       </c>
       <c r="Q81">
-        <v>19.2387628375</v>
+        <v>19.200013</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.2875712028102578</v>
+        <v>0.2988689225677466</v>
       </c>
       <c r="T81">
-        <v>3.518065590140227</v>
+        <v>3.682461178464537</v>
       </c>
       <c r="U81">
         <v>0.0543</v>
@@ -7967,7 +7967,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>6.467973224207843</v>
+        <v>6.387123558905246</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7975,22 +7975,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.09235378451354929</v>
+        <v>0.09214486643694446</v>
       </c>
       <c r="C82">
-        <v>23.24115278909859</v>
+        <v>22.34676909670731</v>
       </c>
       <c r="D82">
-        <v>63.0611527890986</v>
+        <v>63.11826909670733</v>
       </c>
       <c r="E82">
-        <v>71.67</v>
+        <v>72.62150000000001</v>
       </c>
       <c r="F82">
-        <v>76.12</v>
+        <v>77.07150000000001</v>
       </c>
       <c r="G82">
         <v>36.3</v>
@@ -8011,28 +8011,28 @@
         <v>26.4</v>
       </c>
       <c r="M82">
-        <v>4.133316000000001</v>
+        <v>4.184982450000001</v>
       </c>
       <c r="N82">
-        <v>22.266684</v>
+        <v>22.21501755</v>
       </c>
       <c r="O82">
-        <v>5.566670999999999</v>
+        <v>5.5537543875</v>
       </c>
       <c r="P82">
-        <v>16.700013</v>
+        <v>16.6612631625</v>
       </c>
       <c r="Q82">
-        <v>19.200013</v>
+        <v>19.1612631625</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.2988689225677466</v>
+        <v>0.3113558759839183</v>
       </c>
       <c r="T82">
-        <v>3.682461178464537</v>
+        <v>3.864161565559827</v>
       </c>
       <c r="U82">
         <v>0.0543</v>
@@ -8049,7 +8049,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>6.387123558905246</v>
+        <v>6.308270181634811</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8057,22 +8057,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.09214486643694446</v>
+        <v>0.09193594836033961</v>
       </c>
       <c r="C83">
-        <v>22.34676909670731</v>
+        <v>21.45248896189035</v>
       </c>
       <c r="D83">
-        <v>63.11826909670733</v>
+        <v>63.17548896189037</v>
       </c>
       <c r="E83">
-        <v>72.62150000000001</v>
+        <v>73.57300000000001</v>
       </c>
       <c r="F83">
-        <v>77.07150000000001</v>
+        <v>78.02300000000001</v>
       </c>
       <c r="G83">
         <v>36.3</v>
@@ -8093,28 +8093,28 @@
         <v>26.4</v>
       </c>
       <c r="M83">
-        <v>4.184982450000001</v>
+        <v>4.2366489</v>
       </c>
       <c r="N83">
-        <v>22.21501755</v>
+        <v>22.1633511</v>
       </c>
       <c r="O83">
-        <v>5.5537543875</v>
+        <v>5.540837775</v>
       </c>
       <c r="P83">
-        <v>16.6612631625</v>
+        <v>16.622513325</v>
       </c>
       <c r="Q83">
-        <v>19.1612631625</v>
+        <v>19.122513325</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.3113558759839183</v>
+        <v>0.3252302686685535</v>
       </c>
       <c r="T83">
-        <v>3.864161565559827</v>
+        <v>4.066050884554593</v>
       </c>
       <c r="U83">
         <v>0.0543</v>
@@ -8131,7 +8131,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>6.308270181634811</v>
+        <v>6.231340057468533</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8139,22 +8139,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.09193594836033961</v>
+        <v>0.09172703028373477</v>
       </c>
       <c r="C84">
-        <v>21.45248896189035</v>
+        <v>20.5583126665436</v>
       </c>
       <c r="D84">
-        <v>63.17548896189037</v>
+        <v>63.23281266654362</v>
       </c>
       <c r="E84">
-        <v>73.57300000000001</v>
+        <v>74.5245</v>
       </c>
       <c r="F84">
-        <v>78.02300000000001</v>
+        <v>78.97450000000001</v>
       </c>
       <c r="G84">
         <v>36.3</v>
@@ -8175,28 +8175,28 @@
         <v>26.4</v>
       </c>
       <c r="M84">
-        <v>4.2366489</v>
+        <v>4.28831535</v>
       </c>
       <c r="N84">
-        <v>22.1633511</v>
+        <v>22.11168465</v>
       </c>
       <c r="O84">
-        <v>5.540837775</v>
+        <v>5.527921162499999</v>
       </c>
       <c r="P84">
-        <v>16.622513325</v>
+        <v>16.5837634875</v>
       </c>
       <c r="Q84">
-        <v>19.122513325</v>
+        <v>19.0837634875</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.3252302686685535</v>
+        <v>0.3407369428454988</v>
       </c>
       <c r="T84">
-        <v>4.066050884554593</v>
+        <v>4.291691888136979</v>
       </c>
       <c r="U84">
         <v>0.0543</v>
@@ -8213,7 +8213,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>6.231340057468533</v>
+        <v>6.156263671233972</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8221,22 +8221,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.09172703028373477</v>
+        <v>0.09214811220712993</v>
       </c>
       <c r="C85">
-        <v>20.5583126665436</v>
+        <v>19.4913809413586</v>
       </c>
       <c r="D85">
-        <v>63.23281266654362</v>
+        <v>63.11738094135862</v>
       </c>
       <c r="E85">
-        <v>74.5245</v>
+        <v>75.47600000000001</v>
       </c>
       <c r="F85">
-        <v>78.97450000000001</v>
+        <v>79.92600000000002</v>
       </c>
       <c r="G85">
         <v>36.3</v>
@@ -8257,45 +8257,45 @@
         <v>26.4</v>
       </c>
       <c r="M85">
-        <v>4.28831535</v>
+        <v>4.419907800000001</v>
       </c>
       <c r="N85">
-        <v>22.11168465</v>
+        <v>21.9800922</v>
       </c>
       <c r="O85">
-        <v>5.527921162499999</v>
+        <v>5.495023049999999</v>
       </c>
       <c r="P85">
-        <v>16.5837634875</v>
+        <v>16.48506915</v>
       </c>
       <c r="Q85">
-        <v>19.0837634875</v>
+        <v>18.98506915</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.3407369428454988</v>
+        <v>0.3581819512945623</v>
       </c>
       <c r="T85">
-        <v>4.291691888136979</v>
+        <v>4.545538017167164</v>
       </c>
       <c r="U85">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V85">
         <v>0.25</v>
       </c>
       <c r="W85">
-        <v>0.040725</v>
+        <v>0.041475</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y85">
-        <v>6.156263671233972</v>
+        <v>5.972975273375611</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8303,22 +8303,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.09214811220712993</v>
+        <v>0.0919466941305251</v>
       </c>
       <c r="C86">
-        <v>19.49138094135861</v>
+        <v>18.59504330851394</v>
       </c>
       <c r="D86">
-        <v>63.11738094135862</v>
+        <v>63.17254330851393</v>
       </c>
       <c r="E86">
-        <v>75.476</v>
+        <v>76.42749999999999</v>
       </c>
       <c r="F86">
-        <v>79.926</v>
+        <v>80.8775</v>
       </c>
       <c r="G86">
         <v>36.3</v>
@@ -8339,28 +8339,28 @@
         <v>26.4</v>
       </c>
       <c r="M86">
-        <v>4.4199078</v>
+        <v>4.47252575</v>
       </c>
       <c r="N86">
-        <v>21.9800922</v>
+        <v>21.92747425</v>
       </c>
       <c r="O86">
-        <v>5.495023049999999</v>
+        <v>5.4818685625</v>
       </c>
       <c r="P86">
-        <v>16.48506915</v>
+        <v>16.4456056875</v>
       </c>
       <c r="Q86">
-        <v>18.98506915</v>
+        <v>18.9456056875</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.358181951294562</v>
+        <v>0.3779529608701673</v>
       </c>
       <c r="T86">
-        <v>4.545538017167161</v>
+        <v>4.833230296734704</v>
       </c>
       <c r="U86">
         <v>0.0553</v>
@@ -8377,7 +8377,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>5.972975273375612</v>
+        <v>5.902704976041782</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8385,22 +8385,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.0919466941305251</v>
+        <v>0.09174527605392024</v>
       </c>
       <c r="C87">
-        <v>18.59504330851394</v>
+        <v>17.69880217994131</v>
       </c>
       <c r="D87">
-        <v>63.17254330851393</v>
+        <v>63.22780217994132</v>
       </c>
       <c r="E87">
-        <v>76.42749999999999</v>
+        <v>77.379</v>
       </c>
       <c r="F87">
-        <v>80.8775</v>
+        <v>81.82900000000001</v>
       </c>
       <c r="G87">
         <v>36.3</v>
@@ -8421,28 +8421,28 @@
         <v>26.4</v>
       </c>
       <c r="M87">
-        <v>4.47252575</v>
+        <v>4.525143700000001</v>
       </c>
       <c r="N87">
-        <v>21.92747425</v>
+        <v>21.8748563</v>
       </c>
       <c r="O87">
-        <v>5.4818685625</v>
+        <v>5.468714074999999</v>
       </c>
       <c r="P87">
-        <v>16.4456056875</v>
+        <v>16.406142225</v>
       </c>
       <c r="Q87">
-        <v>18.9456056875</v>
+        <v>18.906142225</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.3779529608701673</v>
+        <v>0.4005484003851446</v>
       </c>
       <c r="T87">
-        <v>4.833230296734704</v>
+        <v>5.162021473383322</v>
       </c>
       <c r="U87">
         <v>0.0553</v>
@@ -8459,7 +8459,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>5.902704976041782</v>
+        <v>5.834068871669201</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8467,22 +8467,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.09174527605392024</v>
+        <v>0.0915438579773154</v>
       </c>
       <c r="C88">
-        <v>17.69880217994131</v>
+        <v>16.80265780910786</v>
       </c>
       <c r="D88">
-        <v>63.22780217994132</v>
+        <v>63.28315780910786</v>
       </c>
       <c r="E88">
-        <v>77.379</v>
+        <v>78.3305</v>
       </c>
       <c r="F88">
-        <v>81.82900000000001</v>
+        <v>82.7805</v>
       </c>
       <c r="G88">
         <v>36.3</v>
@@ -8503,28 +8503,28 @@
         <v>26.4</v>
       </c>
       <c r="M88">
-        <v>4.525143700000001</v>
+        <v>4.57776165</v>
       </c>
       <c r="N88">
-        <v>21.8748563</v>
+        <v>21.82223835</v>
       </c>
       <c r="O88">
-        <v>5.468714074999999</v>
+        <v>5.4555595875</v>
       </c>
       <c r="P88">
-        <v>16.406142225</v>
+        <v>16.3666787625</v>
       </c>
       <c r="Q88">
-        <v>18.906142225</v>
+        <v>18.8666787625</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.4005484003851446</v>
+        <v>0.4266200613639646</v>
       </c>
       <c r="T88">
-        <v>5.162021473383322</v>
+        <v>5.541395907977883</v>
       </c>
       <c r="U88">
         <v>0.0553</v>
@@ -8541,7 +8541,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>5.834068871669201</v>
+        <v>5.767010608776452</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8549,22 +8549,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.0915438579773154</v>
+        <v>0.09134243990071056</v>
       </c>
       <c r="C89">
-        <v>16.80265780910786</v>
+        <v>15.90661045036899</v>
       </c>
       <c r="D89">
-        <v>63.28315780910786</v>
+        <v>63.338610450369</v>
       </c>
       <c r="E89">
-        <v>78.3305</v>
+        <v>79.282</v>
       </c>
       <c r="F89">
-        <v>82.7805</v>
+        <v>83.732</v>
       </c>
       <c r="G89">
         <v>36.3</v>
@@ -8585,28 +8585,28 @@
         <v>26.4</v>
       </c>
       <c r="M89">
-        <v>4.57776165</v>
+        <v>4.6303796</v>
       </c>
       <c r="N89">
-        <v>21.82223835</v>
+        <v>21.7696204</v>
       </c>
       <c r="O89">
-        <v>5.4555595875</v>
+        <v>5.442405099999999</v>
       </c>
       <c r="P89">
-        <v>16.3666787625</v>
+        <v>16.3272153</v>
       </c>
       <c r="Q89">
-        <v>18.8666787625</v>
+        <v>18.8272153</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.4266200613639646</v>
+        <v>0.4570369991725881</v>
       </c>
       <c r="T89">
-        <v>5.541395907977883</v>
+        <v>5.983999415004871</v>
       </c>
       <c r="U89">
         <v>0.0553</v>
@@ -8623,7 +8623,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>5.767010608776452</v>
+        <v>5.701476397313083</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8631,22 +8631,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.09134243990071056</v>
+        <v>0.09114102182410572</v>
       </c>
       <c r="C90">
-        <v>15.90661045036899</v>
+        <v>15.01066035897249</v>
       </c>
       <c r="D90">
-        <v>63.338610450369</v>
+        <v>63.3941603589725</v>
       </c>
       <c r="E90">
-        <v>79.282</v>
+        <v>80.23350000000001</v>
       </c>
       <c r="F90">
-        <v>83.732</v>
+        <v>84.68350000000001</v>
       </c>
       <c r="G90">
         <v>36.3</v>
@@ -8667,28 +8667,28 @@
         <v>26.4</v>
       </c>
       <c r="M90">
-        <v>4.6303796</v>
+        <v>4.682997550000001</v>
       </c>
       <c r="N90">
-        <v>21.7696204</v>
+        <v>21.71700245</v>
       </c>
       <c r="O90">
-        <v>5.442405099999999</v>
+        <v>5.4292506125</v>
       </c>
       <c r="P90">
-        <v>16.3272153</v>
+        <v>16.2877518375</v>
       </c>
       <c r="Q90">
-        <v>18.8272153</v>
+        <v>18.7877518375</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.4570369991725881</v>
+        <v>0.492984289310052</v>
       </c>
       <c r="T90">
-        <v>5.983999415004871</v>
+        <v>6.507076286945856</v>
       </c>
       <c r="U90">
         <v>0.0553</v>
@@ -8705,7 +8705,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>5.701476397313083</v>
+        <v>5.637414864759004</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8713,22 +8713,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.09114102182410572</v>
+        <v>0.09093960374750087</v>
       </c>
       <c r="C91">
-        <v>15.01066035897249</v>
+        <v>14.11480779106235</v>
       </c>
       <c r="D91">
-        <v>63.3941603589725</v>
+        <v>63.44980779106236</v>
       </c>
       <c r="E91">
-        <v>80.23350000000001</v>
+        <v>81.185</v>
       </c>
       <c r="F91">
-        <v>84.68350000000001</v>
+        <v>85.63500000000001</v>
       </c>
       <c r="G91">
         <v>36.3</v>
@@ -8749,28 +8749,28 @@
         <v>26.4</v>
       </c>
       <c r="M91">
-        <v>4.682997550000001</v>
+        <v>4.735615500000001</v>
       </c>
       <c r="N91">
-        <v>21.71700245</v>
+        <v>21.6643845</v>
       </c>
       <c r="O91">
-        <v>5.4292506125</v>
+        <v>5.416096124999999</v>
       </c>
       <c r="P91">
-        <v>16.2877518375</v>
+        <v>16.248288375</v>
       </c>
       <c r="Q91">
-        <v>18.7877518375</v>
+        <v>18.748288375</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.492984289310052</v>
+        <v>0.5361210374750089</v>
       </c>
       <c r="T91">
-        <v>6.507076286945856</v>
+        <v>7.13476853327504</v>
       </c>
       <c r="U91">
         <v>0.0553</v>
@@ -8787,7 +8787,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>5.637414864759004</v>
+        <v>5.574776921817237</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8795,22 +8795,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.09093960374750087</v>
+        <v>0.09073818567089602</v>
       </c>
       <c r="C92">
-        <v>14.11480779106235</v>
+        <v>13.21905300368275</v>
       </c>
       <c r="D92">
-        <v>63.44980779106236</v>
+        <v>63.50555300368276</v>
       </c>
       <c r="E92">
-        <v>81.185</v>
+        <v>82.13650000000001</v>
       </c>
       <c r="F92">
-        <v>85.63500000000001</v>
+        <v>86.58650000000002</v>
       </c>
       <c r="G92">
         <v>36.3</v>
@@ -8831,28 +8831,28 @@
         <v>26.4</v>
       </c>
       <c r="M92">
-        <v>4.735615500000001</v>
+        <v>4.788233450000001</v>
       </c>
       <c r="N92">
-        <v>21.6643845</v>
+        <v>21.61176655</v>
       </c>
       <c r="O92">
-        <v>5.416096124999999</v>
+        <v>5.4029416375</v>
       </c>
       <c r="P92">
-        <v>16.248288375</v>
+        <v>16.2088249125</v>
       </c>
       <c r="Q92">
-        <v>18.748288375</v>
+        <v>18.7088249125</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.5361210374750089</v>
+        <v>0.5888437296766227</v>
       </c>
       <c r="T92">
-        <v>7.13476853327504</v>
+        <v>7.901947945455152</v>
       </c>
       <c r="U92">
         <v>0.0553</v>
@@ -8869,7 +8869,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>5.574776921817237</v>
+        <v>5.513515636962103</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8877,22 +8877,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.09073818567089602</v>
+        <v>0.09053676759429119</v>
       </c>
       <c r="C93">
-        <v>13.21905300368275</v>
+        <v>12.32339625478193</v>
       </c>
       <c r="D93">
-        <v>63.50555300368276</v>
+        <v>63.56139625478193</v>
       </c>
       <c r="E93">
-        <v>82.13650000000001</v>
+        <v>83.08800000000001</v>
       </c>
       <c r="F93">
-        <v>86.58650000000002</v>
+        <v>87.53800000000001</v>
       </c>
       <c r="G93">
         <v>36.3</v>
@@ -8913,28 +8913,28 @@
         <v>26.4</v>
       </c>
       <c r="M93">
-        <v>4.788233450000001</v>
+        <v>4.840851400000001</v>
       </c>
       <c r="N93">
-        <v>21.61176655</v>
+        <v>21.5591486</v>
       </c>
       <c r="O93">
-        <v>5.4029416375</v>
+        <v>5.389787149999999</v>
       </c>
       <c r="P93">
-        <v>16.2088249125</v>
+        <v>16.16936145</v>
       </c>
       <c r="Q93">
-        <v>18.7088249125</v>
+        <v>18.66936145</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.5888437296766227</v>
+        <v>0.6547470949286402</v>
       </c>
       <c r="T93">
-        <v>7.901947945455152</v>
+        <v>8.860922210680295</v>
       </c>
       <c r="U93">
         <v>0.0553</v>
@@ -8951,7 +8951,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>5.513515636962103</v>
+        <v>5.453586119169036</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8959,22 +8959,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.09053676759429119</v>
+        <v>0.09033534951768635</v>
       </c>
       <c r="C94">
-        <v>12.32339625478193</v>
+        <v>11.42783780321631</v>
       </c>
       <c r="D94">
-        <v>63.56139625478193</v>
+        <v>63.61733780321632</v>
       </c>
       <c r="E94">
-        <v>83.08800000000001</v>
+        <v>84.0395</v>
       </c>
       <c r="F94">
-        <v>87.53800000000001</v>
+        <v>88.48950000000001</v>
       </c>
       <c r="G94">
         <v>36.3</v>
@@ -8995,28 +8995,28 @@
         <v>26.4</v>
       </c>
       <c r="M94">
-        <v>4.840851400000001</v>
+        <v>4.89346935</v>
       </c>
       <c r="N94">
-        <v>21.5591486</v>
+        <v>21.50653065</v>
       </c>
       <c r="O94">
-        <v>5.389787149999999</v>
+        <v>5.3766326625</v>
       </c>
       <c r="P94">
-        <v>16.16936145</v>
+        <v>16.1298979875</v>
       </c>
       <c r="Q94">
-        <v>18.66936145</v>
+        <v>18.6298979875</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.6547470949286402</v>
+        <v>0.7394799931098055</v>
       </c>
       <c r="T94">
-        <v>8.860922210680295</v>
+        <v>10.09388912311262</v>
       </c>
       <c r="U94">
         <v>0.0553</v>
@@ -9033,7 +9033,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>5.453586119169036</v>
+        <v>5.39494540821023</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9041,22 +9041,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.09033534951768635</v>
+        <v>0.09013393144108151</v>
       </c>
       <c r="C95">
-        <v>11.42783780321631</v>
+        <v>10.53237790875433</v>
       </c>
       <c r="D95">
-        <v>63.61733780321632</v>
+        <v>63.67337790875435</v>
       </c>
       <c r="E95">
-        <v>84.0395</v>
+        <v>84.99100000000001</v>
       </c>
       <c r="F95">
-        <v>88.48950000000001</v>
+        <v>89.44100000000002</v>
       </c>
       <c r="G95">
         <v>36.3</v>
@@ -9077,28 +9077,28 @@
         <v>26.4</v>
       </c>
       <c r="M95">
-        <v>4.89346935</v>
+        <v>4.946087300000001</v>
       </c>
       <c r="N95">
-        <v>21.50653065</v>
+        <v>21.4539127</v>
       </c>
       <c r="O95">
-        <v>5.3766326625</v>
+        <v>5.363478174999999</v>
       </c>
       <c r="P95">
-        <v>16.1298979875</v>
+        <v>16.090434525</v>
       </c>
       <c r="Q95">
-        <v>18.6298979875</v>
+        <v>18.590434525</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.7394799931098055</v>
+        <v>0.8524571906846925</v>
       </c>
       <c r="T95">
-        <v>10.09388912311262</v>
+        <v>11.73784500635572</v>
       </c>
       <c r="U95">
         <v>0.0553</v>
@@ -9115,7 +9115,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>5.39494540821023</v>
+        <v>5.337552371952673</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9123,22 +9123,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.09013393144108151</v>
+        <v>0.08993251336447666</v>
       </c>
       <c r="C96">
-        <v>10.53237790875433</v>
+        <v>9.637016832080604</v>
       </c>
       <c r="D96">
-        <v>63.67337790875435</v>
+        <v>63.72951683208063</v>
       </c>
       <c r="E96">
-        <v>84.99100000000001</v>
+        <v>85.94250000000001</v>
       </c>
       <c r="F96">
-        <v>89.44100000000002</v>
+        <v>90.39250000000001</v>
       </c>
       <c r="G96">
         <v>36.3</v>
@@ -9159,28 +9159,28 @@
         <v>26.4</v>
       </c>
       <c r="M96">
-        <v>4.946087300000001</v>
+        <v>4.99870525</v>
       </c>
       <c r="N96">
-        <v>21.4539127</v>
+        <v>21.40129475</v>
       </c>
       <c r="O96">
-        <v>5.363478174999999</v>
+        <v>5.3503236875</v>
       </c>
       <c r="P96">
-        <v>16.090434525</v>
+        <v>16.0509710625</v>
       </c>
       <c r="Q96">
-        <v>18.590434525</v>
+        <v>18.5509710625</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.8524571906846925</v>
+        <v>1.010625267289535</v>
       </c>
       <c r="T96">
-        <v>11.73784500635572</v>
+        <v>14.03938324289606</v>
       </c>
       <c r="U96">
         <v>0.0553</v>
@@ -9197,7 +9197,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>5.337552371952673</v>
+        <v>5.281367610142646</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9205,22 +9205,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.08993251336447666</v>
+        <v>0.08973109528787183</v>
       </c>
       <c r="C97">
-        <v>9.637016832080604</v>
+        <v>8.74175483479992</v>
       </c>
       <c r="D97">
-        <v>63.72951683208063</v>
+        <v>63.78575483479993</v>
       </c>
       <c r="E97">
-        <v>85.94250000000001</v>
+        <v>86.89400000000001</v>
       </c>
       <c r="F97">
-        <v>90.39250000000001</v>
+        <v>91.34400000000001</v>
       </c>
       <c r="G97">
         <v>36.3</v>
@@ -9241,28 +9241,28 @@
         <v>26.4</v>
       </c>
       <c r="M97">
-        <v>4.99870525</v>
+        <v>5.051323200000001</v>
       </c>
       <c r="N97">
-        <v>21.40129475</v>
+        <v>21.3486768</v>
       </c>
       <c r="O97">
-        <v>5.3503236875</v>
+        <v>5.3371692</v>
       </c>
       <c r="P97">
-        <v>16.0509710625</v>
+        <v>16.0115076</v>
       </c>
       <c r="Q97">
-        <v>18.5509710625</v>
+        <v>18.5115076</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>1.010625267289535</v>
+        <v>1.247877382196798</v>
       </c>
       <c r="T97">
-        <v>14.03938324289606</v>
+        <v>17.49169059770658</v>
       </c>
       <c r="U97">
         <v>0.0553</v>
@@ -9279,7 +9279,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>5.281367610142646</v>
+        <v>5.22635336420366</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9287,22 +9287,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.08973109528787185</v>
+        <v>0.08952967721126699</v>
       </c>
       <c r="C98">
-        <v>8.74175483479992</v>
+        <v>7.846592179441245</v>
       </c>
       <c r="D98">
-        <v>63.78575483479993</v>
+        <v>63.84209217944126</v>
       </c>
       <c r="E98">
-        <v>86.89400000000001</v>
+        <v>87.8455</v>
       </c>
       <c r="F98">
-        <v>91.34400000000001</v>
+        <v>92.2955</v>
       </c>
       <c r="G98">
         <v>36.3</v>
@@ -9323,28 +9323,28 @@
         <v>26.4</v>
       </c>
       <c r="M98">
-        <v>5.051323200000001</v>
+        <v>5.103941150000001</v>
       </c>
       <c r="N98">
-        <v>21.3486768</v>
+        <v>21.29605885</v>
       </c>
       <c r="O98">
-        <v>5.3371692</v>
+        <v>5.324014712499999</v>
       </c>
       <c r="P98">
-        <v>16.0115076</v>
+        <v>15.9720441375</v>
       </c>
       <c r="Q98">
-        <v>18.5115076</v>
+        <v>18.4720441375</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>1.247877382196795</v>
+        <v>1.643297573708898</v>
       </c>
       <c r="T98">
-        <v>17.49169059770653</v>
+        <v>23.24553618905736</v>
       </c>
       <c r="U98">
         <v>0.0553</v>
@@ -9361,7 +9361,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>5.22635336420366</v>
+        <v>5.172473432613931</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9369,22 +9369,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.08952967721126699</v>
+        <v>0.08932825913466214</v>
       </c>
       <c r="C99">
-        <v>7.846592179441245</v>
+        <v>6.951529129461903</v>
       </c>
       <c r="D99">
-        <v>63.84209217944126</v>
+        <v>63.89852912946191</v>
       </c>
       <c r="E99">
-        <v>87.8455</v>
+        <v>88.797</v>
       </c>
       <c r="F99">
-        <v>92.2955</v>
+        <v>93.247</v>
       </c>
       <c r="G99">
         <v>36.3</v>
@@ -9405,28 +9405,28 @@
         <v>26.4</v>
       </c>
       <c r="M99">
-        <v>5.103941150000001</v>
+        <v>5.1565591</v>
       </c>
       <c r="N99">
-        <v>21.29605885</v>
+        <v>21.2434409</v>
       </c>
       <c r="O99">
-        <v>5.324014712499999</v>
+        <v>5.310860225</v>
       </c>
       <c r="P99">
-        <v>15.9720441375</v>
+        <v>15.932580675</v>
       </c>
       <c r="Q99">
-        <v>18.4720441375</v>
+        <v>18.432580675</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.643297573708898</v>
+        <v>2.434137956733105</v>
       </c>
       <c r="T99">
-        <v>23.24553618905736</v>
+        <v>34.75322737175903</v>
       </c>
       <c r="U99">
         <v>0.0553</v>
@@ -9443,7 +9443,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>5.172473432613931</v>
+        <v>5.119693091464811</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9451,22 +9451,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.08932825913466214</v>
+        <v>0.08912684105805731</v>
       </c>
       <c r="C100">
-        <v>6.951529129461903</v>
+        <v>6.056565949251549</v>
       </c>
       <c r="D100">
-        <v>63.89852912946191</v>
+        <v>63.95506594925155</v>
       </c>
       <c r="E100">
-        <v>88.797</v>
+        <v>89.74850000000001</v>
       </c>
       <c r="F100">
-        <v>93.247</v>
+        <v>94.19850000000001</v>
       </c>
       <c r="G100">
         <v>36.3</v>
@@ -9487,28 +9487,28 @@
         <v>26.4</v>
       </c>
       <c r="M100">
-        <v>5.1565591</v>
+        <v>5.209177050000001</v>
       </c>
       <c r="N100">
-        <v>21.2434409</v>
+        <v>21.19082295</v>
       </c>
       <c r="O100">
-        <v>5.310860225</v>
+        <v>5.297705737499999</v>
       </c>
       <c r="P100">
-        <v>15.932580675</v>
+        <v>15.8931172125</v>
       </c>
       <c r="Q100">
-        <v>18.432580675</v>
+        <v>18.3931172125</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>2.434137956733105</v>
+        <v>4.806659105805727</v>
       </c>
       <c r="T100">
-        <v>34.75322737175903</v>
+        <v>69.27630091986403</v>
       </c>
       <c r="U100">
         <v>0.0553</v>
@@ -9525,91 +9525,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>5.119693091464811</v>
+        <v>5.067979019833851</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.08912684105805731</v>
-      </c>
-      <c r="C101">
-        <v>6.056565949251549</v>
-      </c>
-      <c r="D101">
-        <v>63.95506594925155</v>
-      </c>
-      <c r="E101">
-        <v>89.74850000000001</v>
-      </c>
-      <c r="F101">
-        <v>94.19850000000001</v>
-      </c>
-      <c r="G101">
-        <v>36.3</v>
-      </c>
-      <c r="H101">
-        <v>90.7</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>28.9</v>
-      </c>
-      <c r="K101">
-        <v>2.5</v>
-      </c>
-      <c r="L101">
-        <v>26.4</v>
-      </c>
-      <c r="M101">
-        <v>5.209177050000001</v>
-      </c>
-      <c r="N101">
-        <v>21.19082295</v>
-      </c>
-      <c r="O101">
-        <v>5.297705737499999</v>
-      </c>
-      <c r="P101">
-        <v>15.8931172125</v>
-      </c>
-      <c r="Q101">
-        <v>18.3931172125</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>4.806659105805727</v>
-      </c>
-      <c r="T101">
-        <v>69.27630091986403</v>
-      </c>
-      <c r="U101">
-        <v>0.0553</v>
-      </c>
-      <c r="V101">
-        <v>0.25</v>
-      </c>
-      <c r="W101">
-        <v>0.041475</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>A3/A-</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>5.067979019833851</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
